--- a/public/planilhas/04_regua_cobranca_inteligente.xlsx
+++ b/public/planilhas/04_regua_cobranca_inteligente.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONTAS" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'DASHBOARD'!$A$1:$L$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'DASHBOARD'!$A$1:$R$60</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,12 +19,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="&quot;R$&quot; #,##0"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yy"/>
+    <numFmt numFmtId="167" formatCode="#,##0;(#,##0);&quot;—&quot;"/>
+    <numFmt numFmtId="168" formatCode="#,##0.0;(#,##0.0);&quot;—&quot;"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -108,6 +110,37 @@
       <color rgb="00C99C66"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <color rgb="008A9691"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <color rgb="00C99C66"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <b val="1"/>
+      <color rgb="008A9691"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <color rgb="0043D07F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <color rgb="008A9691"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <color rgb="0043D07F"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -158,7 +191,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -197,14 +230,44 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="14" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="15" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="13" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="18" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <name val="Aptos Narrow"/>
+        <b val="1"/>
+        <color rgb="0043D07F"/>
+        <sz val="9"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Aptos Narrow"/>
+        <b val="1"/>
+        <color rgb="00D9534F"/>
+        <sz val="9"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <name val="Aptos Narrow"/>
@@ -374,6 +437,219 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Cascata · a receber → esperado</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'DASHBOARD'!C21</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'DASHBOARD'!$B$22:$B$24</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'DASHBOARD'!$C$22:$C$24</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'DASHBOARD'!D21</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="2E9E5B"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'DASHBOARD'!$B$22:$B$24</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'DASHBOARD'!$D$22:$D$24</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'DASHBOARD'!E21</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="D9534F"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'DASHBOARD'!$B$22:$B$24</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'DASHBOARD'!$E$22:$E$24</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <overlap val="100"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'DASHBOARD'!O21</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="15000">
+              <a:solidFill>
+                <a:srgbClr val="C99C66"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'DASHBOARD'!$N$22:$N$26</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'DASHBOARD'!$O$22:$O$26</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -393,6 +669,50 @@
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4320000" cy="2340000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>29</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3600000" cy="1440000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -690,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L55"/>
+  <dimension ref="A1:Z55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -812,27 +1132,27 @@
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="2" t="n"/>
       <c r="B6" s="7">
-        <f>B40</f>
+        <f>Z40</f>
         <v/>
       </c>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="8">
-        <f>B41</f>
+        <f>Z41</f>
         <v/>
       </c>
       <c r="E6" s="6" t="n"/>
       <c r="F6" s="9">
-        <f>B42</f>
+        <f>Z42</f>
         <v/>
       </c>
       <c r="G6" s="6" t="n"/>
       <c r="H6" s="10">
-        <f>B44</f>
+        <f>Z44</f>
         <v/>
       </c>
       <c r="I6" s="6" t="n"/>
       <c r="J6" s="8">
-        <f>B40-B42</f>
+        <f>Z40-Z42</f>
         <v/>
       </c>
       <c r="K6" s="6" t="n"/>
@@ -1077,7 +1397,11 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n"/>
-      <c r="B20" s="2" t="n"/>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>Cascata da carteira</t>
+        </is>
+      </c>
       <c r="C20" s="2" t="n"/>
       <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="n"/>
@@ -1088,62 +1412,200 @@
       <c r="J20" s="2" t="n"/>
       <c r="K20" s="2" t="n"/>
       <c r="L20" s="2" t="n"/>
-    </row>
-    <row r="21">
+      <c r="N20" s="16" t="inlineStr">
+        <is>
+          <t>Spark · aging</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
       <c r="A21" s="2" t="n"/>
-      <c r="B21" s="2" t="n"/>
-      <c r="C21" s="2" t="n"/>
-      <c r="D21" s="2" t="n"/>
-      <c r="E21" s="2" t="n"/>
-      <c r="F21" s="2" t="n"/>
-      <c r="G21" s="2" t="n"/>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>Etapa</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>Baixa</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>Δ</t>
+        </is>
+      </c>
       <c r="H21" s="2" t="n"/>
       <c r="I21" s="2" t="n"/>
       <c r="J21" s="2" t="n"/>
       <c r="K21" s="2" t="n"/>
       <c r="L21" s="2" t="n"/>
+      <c r="N21" s="13" t="inlineStr">
+        <is>
+          <t>Ponto</t>
+        </is>
+      </c>
+      <c r="O21" s="13" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="P21" s="17" t="inlineStr">
+        <is>
+          <t>Spark</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n"/>
-      <c r="B22" s="2" t="n"/>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="n"/>
-      <c r="E22" s="2" t="n"/>
-      <c r="F22" s="2" t="n"/>
-      <c r="G22" s="2" t="n"/>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>A receber</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="18">
+        <f>IF(G22&gt;=0,G22,0)</f>
+        <v/>
+      </c>
+      <c r="E22" s="18">
+        <f>IF(G22&lt;0,-G22,0)</f>
+        <v/>
+      </c>
+      <c r="F22" s="18">
+        <f>G22</f>
+        <v/>
+      </c>
+      <c r="G22" s="19">
+        <f>$Z$40</f>
+        <v/>
+      </c>
       <c r="H22" s="2" t="n"/>
       <c r="I22" s="2" t="n"/>
       <c r="J22" s="2" t="n"/>
       <c r="K22" s="2" t="n"/>
       <c r="L22" s="2" t="n"/>
+      <c r="N22" s="20" t="inlineStr">
+        <is>
+          <t>A vencer</t>
+        </is>
+      </c>
+      <c r="O22" s="21">
+        <f>C11</f>
+        <v/>
+      </c>
+      <c r="P22" s="22">
+        <f>IF(OR(O22="",NOT(ISNUMBER(O22))),"",REPT("▬",MAX(1,ROUND((O22-(MIN(O22:O26)))/MAX(1E-9,(MAX(O22:O26))-(MIN(O22:O26)))*10,0))))</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n"/>
-      <c r="B23" s="2" t="n"/>
-      <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="n"/>
-      <c r="E23" s="2" t="n"/>
-      <c r="F23" s="2" t="n"/>
-      <c r="G23" s="2" t="n"/>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>− Perda potencial</t>
+        </is>
+      </c>
+      <c r="C23" s="18">
+        <f>IF(G23&gt;=0,F22,F22+G23)</f>
+        <v/>
+      </c>
+      <c r="D23" s="18">
+        <f>IF(G23&gt;=0,G23,0)</f>
+        <v/>
+      </c>
+      <c r="E23" s="18">
+        <f>IF(G23&lt;0,-G23,0)</f>
+        <v/>
+      </c>
+      <c r="F23" s="18">
+        <f>F22+G23</f>
+        <v/>
+      </c>
+      <c r="G23" s="19">
+        <f>-($Z$40-$Z$42)</f>
+        <v/>
+      </c>
       <c r="H23" s="2" t="n"/>
       <c r="I23" s="2" t="n"/>
       <c r="J23" s="2" t="n"/>
       <c r="K23" s="2" t="n"/>
       <c r="L23" s="2" t="n"/>
+      <c r="N23" s="20" t="inlineStr">
+        <is>
+          <t>1-30</t>
+        </is>
+      </c>
+      <c r="O23" s="21">
+        <f>C12</f>
+        <v/>
+      </c>
+      <c r="P23" s="22">
+        <f>IF(OR(O23="",NOT(ISNUMBER(O23))),"",REPT("▬",MAX(1,ROUND((O23-(MIN(O22:O26)))/MAX(1E-9,(MAX(O22:O26))-(MIN(O22:O26)))*10,0))))</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n"/>
-      <c r="B24" s="2" t="n"/>
-      <c r="C24" s="2" t="n"/>
-      <c r="D24" s="2" t="n"/>
-      <c r="E24" s="2" t="n"/>
-      <c r="F24" s="2" t="n"/>
-      <c r="G24" s="2" t="n"/>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>Recuperação esperada</t>
+        </is>
+      </c>
+      <c r="C24" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="18">
+        <f>IF(G24&gt;=0,G24,0)</f>
+        <v/>
+      </c>
+      <c r="E24" s="18">
+        <f>IF(G24&lt;0,-G24,0)</f>
+        <v/>
+      </c>
+      <c r="F24" s="18">
+        <f>G24</f>
+        <v/>
+      </c>
+      <c r="G24" s="19">
+        <f>$Z$42</f>
+        <v/>
+      </c>
       <c r="H24" s="2" t="n"/>
       <c r="I24" s="2" t="n"/>
       <c r="J24" s="2" t="n"/>
       <c r="K24" s="2" t="n"/>
       <c r="L24" s="2" t="n"/>
+      <c r="N24" s="20" t="inlineStr">
+        <is>
+          <t>31-60</t>
+        </is>
+      </c>
+      <c r="O24" s="21">
+        <f>C13</f>
+        <v/>
+      </c>
+      <c r="P24" s="22">
+        <f>IF(OR(O24="",NOT(ISNUMBER(O24))),"",REPT("▬",MAX(1,ROUND((O24-(MIN(O22:O26)))/MAX(1E-9,(MAX(O22:O26))-(MIN(O22:O26)))*10,0))))</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n"/>
@@ -1158,6 +1620,19 @@
       <c r="J25" s="2" t="n"/>
       <c r="K25" s="2" t="n"/>
       <c r="L25" s="2" t="n"/>
+      <c r="N25" s="20" t="inlineStr">
+        <is>
+          <t>61-90</t>
+        </is>
+      </c>
+      <c r="O25" s="21">
+        <f>C14</f>
+        <v/>
+      </c>
+      <c r="P25" s="22">
+        <f>IF(OR(O25="",NOT(ISNUMBER(O25))),"",REPT("▬",MAX(1,ROUND((O25-(MIN(O22:O26)))/MAX(1E-9,(MAX(O22:O26))-(MIN(O22:O26)))*10,0))))</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n"/>
@@ -1172,6 +1647,19 @@
       <c r="J26" s="2" t="n"/>
       <c r="K26" s="2" t="n"/>
       <c r="L26" s="2" t="n"/>
+      <c r="N26" s="20" t="inlineStr">
+        <is>
+          <t>90+</t>
+        </is>
+      </c>
+      <c r="O26" s="21">
+        <f>C15</f>
+        <v/>
+      </c>
+      <c r="P26" s="22">
+        <f>IF(OR(O26="",NOT(ISNUMBER(O26))),"",REPT("▬",MAX(1,ROUND((O26-(MIN(O22:O26)))/MAX(1E-9,(MAX(O22:O26))-(MIN(O22:O26)))*10,0))))</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n"/>
@@ -1217,7 +1705,11 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n"/>
-      <c r="B30" s="2" t="n"/>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>MINI-SPARKLINES</t>
+        </is>
+      </c>
       <c r="C30" s="2" t="n"/>
       <c r="D30" s="2" t="n"/>
       <c r="E30" s="2" t="n"/>
@@ -1229,59 +1721,164 @@
       <c r="K30" s="2" t="n"/>
       <c r="L30" s="2" t="n"/>
     </row>
-    <row r="31">
+    <row r="31" ht="26" customHeight="1">
       <c r="A31" s="2" t="n"/>
-      <c r="B31" s="2" t="n"/>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2" t="n"/>
-      <c r="E31" s="2" t="n"/>
-      <c r="F31" s="2" t="n"/>
-      <c r="G31" s="2" t="n"/>
-      <c r="H31" s="2" t="n"/>
-      <c r="I31" s="2" t="n"/>
-      <c r="J31" s="2" t="n"/>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>Indicador</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>Atual</t>
+        </is>
+      </c>
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="F31" s="13" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="G31" s="13" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="H31" s="13" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="I31" s="13" t="inlineStr">
+        <is>
+          <t>S6</t>
+        </is>
+      </c>
+      <c r="J31" s="13" t="inlineStr">
+        <is>
+          <t>Spark</t>
+        </is>
+      </c>
       <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n"/>
-      <c r="B32" s="2" t="n"/>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2" t="n"/>
-      <c r="E32" s="2" t="n"/>
-      <c r="F32" s="2" t="n"/>
-      <c r="G32" s="2" t="n"/>
-      <c r="H32" s="2" t="n"/>
-      <c r="I32" s="2" t="n"/>
-      <c r="J32" s="2" t="n"/>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>DSO dias</t>
+        </is>
+      </c>
+      <c r="C32" s="23">
+        <f>$Z$44</f>
+        <v/>
+      </c>
+      <c r="D32" s="24" t="n">
+        <v>45</v>
+      </c>
+      <c r="E32" s="24" t="n">
+        <v>40</v>
+      </c>
+      <c r="F32" s="24" t="n">
+        <v>36</v>
+      </c>
+      <c r="G32" s="24" t="n">
+        <v>33</v>
+      </c>
+      <c r="H32" s="24" t="n">
+        <v>31</v>
+      </c>
+      <c r="I32" s="24">
+        <f>$Z$44</f>
+        <v/>
+      </c>
+      <c r="J32" s="25">
+        <f>IF(D32=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((D32-(MIN(D32:I32)))/MAX(1E-9,(MAX(D32:I32))-(MIN(D32:I32)))*7+1,0))),1))&amp;IF(E32=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((E32-(MIN(D32:I32)))/MAX(1E-9,(MAX(D32:I32))-(MIN(D32:I32)))*7+1,0))),1))&amp;IF(F32=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((F32-(MIN(D32:I32)))/MAX(1E-9,(MAX(D32:I32))-(MIN(D32:I32)))*7+1,0))),1))&amp;IF(G32=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((G32-(MIN(D32:I32)))/MAX(1E-9,(MAX(D32:I32))-(MIN(D32:I32)))*7+1,0))),1))&amp;IF(H32=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((H32-(MIN(D32:I32)))/MAX(1E-9,(MAX(D32:I32))-(MIN(D32:I32)))*7+1,0))),1))&amp;IF(I32=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((I32-(MIN(D32:I32)))/MAX(1E-9,(MAX(D32:I32))-(MIN(D32:I32)))*7+1,0))),1))</f>
+        <v/>
+      </c>
       <c r="K32" s="2" t="n"/>
       <c r="L32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n"/>
-      <c r="B33" s="2" t="n"/>
-      <c r="C33" s="2" t="n"/>
-      <c r="D33" s="2" t="n"/>
-      <c r="E33" s="2" t="n"/>
-      <c r="F33" s="2" t="n"/>
-      <c r="G33" s="2" t="n"/>
-      <c r="H33" s="2" t="n"/>
-      <c r="I33" s="2" t="n"/>
-      <c r="J33" s="2" t="n"/>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>Em atraso</t>
+        </is>
+      </c>
+      <c r="C33" s="23">
+        <f>$Z$41</f>
+        <v/>
+      </c>
+      <c r="D33" s="24" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E33" s="24" t="n">
+        <v>28000</v>
+      </c>
+      <c r="F33" s="24" t="n">
+        <v>26000</v>
+      </c>
+      <c r="G33" s="24" t="n">
+        <v>24000</v>
+      </c>
+      <c r="H33" s="24" t="n">
+        <v>23000</v>
+      </c>
+      <c r="I33" s="24">
+        <f>$Z$41</f>
+        <v/>
+      </c>
+      <c r="J33" s="25">
+        <f>IF(D33=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((D33-(MIN(D33:I33)))/MAX(1E-9,(MAX(D33:I33))-(MIN(D33:I33)))*7+1,0))),1))&amp;IF(E33=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((E33-(MIN(D33:I33)))/MAX(1E-9,(MAX(D33:I33))-(MIN(D33:I33)))*7+1,0))),1))&amp;IF(F33=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((F33-(MIN(D33:I33)))/MAX(1E-9,(MAX(D33:I33))-(MIN(D33:I33)))*7+1,0))),1))&amp;IF(G33=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((G33-(MIN(D33:I33)))/MAX(1E-9,(MAX(D33:I33))-(MIN(D33:I33)))*7+1,0))),1))&amp;IF(H33=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((H33-(MIN(D33:I33)))/MAX(1E-9,(MAX(D33:I33))-(MIN(D33:I33)))*7+1,0))),1))&amp;IF(I33=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((I33-(MIN(D33:I33)))/MAX(1E-9,(MAX(D33:I33))-(MIN(D33:I33)))*7+1,0))),1))</f>
+        <v/>
+      </c>
       <c r="K33" s="2" t="n"/>
       <c r="L33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n"/>
-      <c r="B34" s="2" t="n"/>
-      <c r="C34" s="2" t="n"/>
-      <c r="D34" s="2" t="n"/>
-      <c r="E34" s="2" t="n"/>
-      <c r="F34" s="2" t="n"/>
-      <c r="G34" s="2" t="n"/>
-      <c r="H34" s="2" t="n"/>
-      <c r="I34" s="2" t="n"/>
-      <c r="J34" s="2" t="n"/>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>Esperado</t>
+        </is>
+      </c>
+      <c r="C34" s="23">
+        <f>$Z$42</f>
+        <v/>
+      </c>
+      <c r="D34" s="24" t="n">
+        <v>18000</v>
+      </c>
+      <c r="E34" s="24" t="n">
+        <v>19000</v>
+      </c>
+      <c r="F34" s="24" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G34" s="24" t="n">
+        <v>21000</v>
+      </c>
+      <c r="H34" s="24" t="n">
+        <v>21500</v>
+      </c>
+      <c r="I34" s="24">
+        <f>$Z$42</f>
+        <v/>
+      </c>
+      <c r="J34" s="25">
+        <f>IF(D34=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((D34-(MIN(D34:I34)))/MAX(1E-9,(MAX(D34:I34))-(MIN(D34:I34)))*7+1,0))),1))&amp;IF(E34=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((E34-(MIN(D34:I34)))/MAX(1E-9,(MAX(D34:I34))-(MIN(D34:I34)))*7+1,0))),1))&amp;IF(F34=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((F34-(MIN(D34:I34)))/MAX(1E-9,(MAX(D34:I34))-(MIN(D34:I34)))*7+1,0))),1))&amp;IF(G34=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((G34-(MIN(D34:I34)))/MAX(1E-9,(MAX(D34:I34))-(MIN(D34:I34)))*7+1,0))),1))&amp;IF(H34=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((H34-(MIN(D34:I34)))/MAX(1E-9,(MAX(D34:I34))-(MIN(D34:I34)))*7+1,0))),1))&amp;IF(I34=""," ",MID("▁▂▃▄▅▆▇█",MAX(1,MIN(8,ROUND((I34-(MIN(D34:I34)))/MAX(1E-9,(MAX(D34:I34))-(MIN(D34:I34)))*7+1,0))),1))</f>
+        <v/>
+      </c>
       <c r="K34" s="2" t="n"/>
       <c r="L34" s="2" t="n"/>
     </row>
@@ -1357,10 +1954,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="n"/>
-      <c r="B40" s="16">
-        <f>SUMIF(CONTAS!F:F,"Em aberto",CONTAS!C:C)</f>
-        <v/>
-      </c>
+      <c r="B40" s="2" t="n"/>
       <c r="C40" s="2" t="n"/>
       <c r="D40" s="2" t="n"/>
       <c r="E40" s="2" t="n"/>
@@ -1371,13 +1965,14 @@
       <c r="J40" s="2" t="n"/>
       <c r="K40" s="2" t="n"/>
       <c r="L40" s="2" t="n"/>
+      <c r="Z40" s="26">
+        <f>SUMIF(CONTAS!F:F,"Em aberto",CONTAS!C:C)</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n"/>
-      <c r="B41" s="16">
-        <f>SUMIFS(CONTAS!C:C,CONTAS!F:F,"Em aberto",CONTAS!E:E,"&lt;"&amp;TODAY())</f>
-        <v/>
-      </c>
+      <c r="B41" s="2" t="n"/>
       <c r="C41" s="2" t="n"/>
       <c r="D41" s="2" t="n"/>
       <c r="E41" s="2" t="n"/>
@@ -1388,13 +1983,14 @@
       <c r="J41" s="2" t="n"/>
       <c r="K41" s="2" t="n"/>
       <c r="L41" s="2" t="n"/>
+      <c r="Z41" s="26">
+        <f>SUMIFS(CONTAS!C:C,CONTAS!F:F,"Em aberto",CONTAS!E:E,"&lt;"&amp;TODAY())</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n"/>
-      <c r="B42" s="16">
-        <f>SUMIF(CONTAS!F:F,"Em aberto",CONTAS!J:J)</f>
-        <v/>
-      </c>
+      <c r="B42" s="2" t="n"/>
       <c r="C42" s="2" t="n"/>
       <c r="D42" s="2" t="n"/>
       <c r="E42" s="2" t="n"/>
@@ -1405,13 +2001,14 @@
       <c r="J42" s="2" t="n"/>
       <c r="K42" s="2" t="n"/>
       <c r="L42" s="2" t="n"/>
+      <c r="Z42" s="26">
+        <f>SUMIF(CONTAS!F:F,"Em aberto",CONTAS!J:J)</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n"/>
-      <c r="B43" s="16">
-        <f>COUNTIFS(CONTAS!F:F,"Em aberto",CONTAS!E:E,"&lt;"&amp;TODAY())</f>
-        <v/>
-      </c>
+      <c r="B43" s="2" t="n"/>
       <c r="C43" s="2" t="n"/>
       <c r="D43" s="2" t="n"/>
       <c r="E43" s="2" t="n"/>
@@ -1422,13 +2019,14 @@
       <c r="J43" s="2" t="n"/>
       <c r="K43" s="2" t="n"/>
       <c r="L43" s="2" t="n"/>
+      <c r="Z43" s="26">
+        <f>COUNTIFS(CONTAS!F:F,"Em aberto",CONTAS!E:E,"&lt;"&amp;TODAY())</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n"/>
-      <c r="B44" s="16">
-        <f>IFERROR(SUMPRODUCT((CONTAS!F6:F156="Em aberto")*CONTAS!C6:C156*CONTAS!G6:G156)/SUMIF(CONTAS!F:F,"Em aberto",CONTAS!C:C),0)</f>
-        <v/>
-      </c>
+      <c r="B44" s="2" t="n"/>
       <c r="C44" s="2" t="n"/>
       <c r="D44" s="2" t="n"/>
       <c r="E44" s="2" t="n"/>
@@ -1439,6 +2037,10 @@
       <c r="J44" s="2" t="n"/>
       <c r="K44" s="2" t="n"/>
       <c r="L44" s="2" t="n"/>
+      <c r="Z44" s="26">
+        <f>IFERROR(SUMPRODUCT((CONTAS!F6:F156="Em aberto")*CONTAS!C6:C156*CONTAS!G6:G156)/SUMIF(CONTAS!F:F,"Em aberto",CONTAS!C:C),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n"/>
@@ -1621,6 +2223,23 @@
         <cfvo type="min"/>
         <cfvo type="max"/>
         <color rgb="00E0A94B"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G22:G24">
+    <cfRule type="cellIs" priority="2" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C32:C34">
+    <cfRule type="dataBar" priority="4">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="00C99C66"/>
       </dataBar>
     </cfRule>
   </conditionalFormatting>
@@ -1792,10 +2411,10 @@
       <c r="C6" s="15" t="n">
         <v>1800</v>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="27" t="n">
         <v>46185</v>
       </c>
-      <c r="E6" s="17" t="n">
+      <c r="E6" s="27" t="n">
         <v>46213</v>
       </c>
       <c r="F6" s="14" t="inlineStr">
@@ -1811,7 +2430,7 @@
         <f>IF(F6="Pago","Pago",IF(G6=0,"A vencer",IF(G6&lt;=30,"1-30",IF(G6&lt;=60,"31-60",IF(G6&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I6" s="18">
+      <c r="I6" s="28">
         <f>IF(F6="Pago",1,IF(G6=0,0.97,IF(G6&lt;=30,0.9,IF(G6&lt;=60,0.72,IF(G6&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -1839,10 +2458,10 @@
       <c r="C7" s="15" t="n">
         <v>5200</v>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="27" t="n">
         <v>46195</v>
       </c>
-      <c r="E7" s="17" t="n">
+      <c r="E7" s="27" t="n">
         <v>46221</v>
       </c>
       <c r="F7" s="14" t="inlineStr">
@@ -1858,7 +2477,7 @@
         <f>IF(F7="Pago","Pago",IF(G7=0,"A vencer",IF(G7&lt;=30,"1-30",IF(G7&lt;=60,"31-60",IF(G7&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I7" s="18">
+      <c r="I7" s="28">
         <f>IF(F7="Pago",1,IF(G7=0,0.97,IF(G7&lt;=30,0.9,IF(G7&lt;=60,0.72,IF(G7&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -1886,10 +2505,10 @@
       <c r="C8" s="15" t="n">
         <v>2400</v>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="27" t="n">
         <v>46205</v>
       </c>
-      <c r="E8" s="17" t="n">
+      <c r="E8" s="27" t="n">
         <v>46227</v>
       </c>
       <c r="F8" s="14" t="inlineStr">
@@ -1905,7 +2524,7 @@
         <f>IF(F8="Pago","Pago",IF(G8=0,"A vencer",IF(G8&lt;=30,"1-30",IF(G8&lt;=60,"31-60",IF(G8&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I8" s="18">
+      <c r="I8" s="28">
         <f>IF(F8="Pago",1,IF(G8=0,0.97,IF(G8&lt;=30,0.9,IF(G8&lt;=60,0.72,IF(G8&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -1933,10 +2552,10 @@
       <c r="C9" s="15" t="n">
         <v>980</v>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="27" t="n">
         <v>46210</v>
       </c>
-      <c r="E9" s="17" t="n">
+      <c r="E9" s="27" t="n">
         <v>46234</v>
       </c>
       <c r="F9" s="14" t="inlineStr">
@@ -1952,7 +2571,7 @@
         <f>IF(F9="Pago","Pago",IF(G9=0,"A vencer",IF(G9&lt;=30,"1-30",IF(G9&lt;=60,"31-60",IF(G9&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I9" s="18">
+      <c r="I9" s="28">
         <f>IF(F9="Pago",1,IF(G9=0,0.97,IF(G9&lt;=30,0.9,IF(G9&lt;=60,0.72,IF(G9&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -1980,10 +2599,10 @@
       <c r="C10" s="15" t="n">
         <v>650</v>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="27" t="n">
         <v>46190</v>
       </c>
-      <c r="E10" s="17" t="n">
+      <c r="E10" s="27" t="n">
         <v>46224</v>
       </c>
       <c r="F10" s="14" t="inlineStr">
@@ -1999,7 +2618,7 @@
         <f>IF(F10="Pago","Pago",IF(G10=0,"A vencer",IF(G10&lt;=30,"1-30",IF(G10&lt;=60,"31-60",IF(G10&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I10" s="18">
+      <c r="I10" s="28">
         <f>IF(F10="Pago",1,IF(G10=0,0.97,IF(G10&lt;=30,0.9,IF(G10&lt;=60,0.72,IF(G10&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -2027,10 +2646,10 @@
       <c r="C11" s="15" t="n">
         <v>3600</v>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D11" s="27" t="n">
         <v>46155</v>
       </c>
-      <c r="E11" s="17" t="n">
+      <c r="E11" s="27" t="n">
         <v>46177</v>
       </c>
       <c r="F11" s="14" t="inlineStr">
@@ -2046,7 +2665,7 @@
         <f>IF(F11="Pago","Pago",IF(G11=0,"A vencer",IF(G11&lt;=30,"1-30",IF(G11&lt;=60,"31-60",IF(G11&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I11" s="18">
+      <c r="I11" s="28">
         <f>IF(F11="Pago",1,IF(G11=0,0.97,IF(G11&lt;=30,0.9,IF(G11&lt;=60,0.72,IF(G11&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -2074,10 +2693,10 @@
       <c r="C12" s="15" t="n">
         <v>7800</v>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="27" t="n">
         <v>46175</v>
       </c>
-      <c r="E12" s="17" t="n">
+      <c r="E12" s="27" t="n">
         <v>46200</v>
       </c>
       <c r="F12" s="14" t="inlineStr">
@@ -2093,7 +2712,7 @@
         <f>IF(F12="Pago","Pago",IF(G12=0,"A vencer",IF(G12&lt;=30,"1-30",IF(G12&lt;=60,"31-60",IF(G12&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I12" s="18">
+      <c r="I12" s="28">
         <f>IF(F12="Pago",1,IF(G12=0,0.97,IF(G12&lt;=30,0.9,IF(G12&lt;=60,0.72,IF(G12&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -2121,10 +2740,10 @@
       <c r="C13" s="15" t="n">
         <v>4200</v>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D13" s="27" t="n">
         <v>46130</v>
       </c>
-      <c r="E13" s="17" t="n">
+      <c r="E13" s="27" t="n">
         <v>46130</v>
       </c>
       <c r="F13" s="14" t="inlineStr">
@@ -2140,7 +2759,7 @@
         <f>IF(F13="Pago","Pago",IF(G13=0,"A vencer",IF(G13&lt;=30,"1-30",IF(G13&lt;=60,"31-60",IF(G13&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I13" s="18">
+      <c r="I13" s="28">
         <f>IF(F13="Pago",1,IF(G13=0,0.97,IF(G13&lt;=30,0.9,IF(G13&lt;=60,0.72,IF(G13&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -2168,10 +2787,10 @@
       <c r="C14" s="15" t="n">
         <v>1500</v>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="27" t="n">
         <v>46215</v>
       </c>
-      <c r="E14" s="17" t="n">
+      <c r="E14" s="27" t="n">
         <v>46245</v>
       </c>
       <c r="F14" s="14" t="inlineStr">
@@ -2187,7 +2806,7 @@
         <f>IF(F14="Pago","Pago",IF(G14=0,"A vencer",IF(G14&lt;=30,"1-30",IF(G14&lt;=60,"31-60",IF(G14&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I14" s="18">
+      <c r="I14" s="28">
         <f>IF(F14="Pago",1,IF(G14=0,0.97,IF(G14&lt;=30,0.9,IF(G14&lt;=60,0.72,IF(G14&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -2205,8 +2824,8 @@
       <c r="A15" s="14" t="n"/>
       <c r="B15" s="14" t="n"/>
       <c r="C15" s="15" t="n"/>
-      <c r="D15" s="17" t="n"/>
-      <c r="E15" s="17" t="n"/>
+      <c r="D15" s="27" t="n"/>
+      <c r="E15" s="27" t="n"/>
       <c r="F15" s="14" t="n"/>
       <c r="G15" s="14">
         <f>IF(OR(F15="Pago",E15="",E15&gt;=TODAY()),0,TODAY()-E15)</f>
@@ -2216,7 +2835,7 @@
         <f>IF(F15="Pago","Pago",IF(G15=0,"A vencer",IF(G15&lt;=30,"1-30",IF(G15&lt;=60,"31-60",IF(G15&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I15" s="18">
+      <c r="I15" s="28">
         <f>IF(F15="Pago",1,IF(G15=0,0.97,IF(G15&lt;=30,0.9,IF(G15&lt;=60,0.72,IF(G15&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -2234,8 +2853,8 @@
       <c r="A16" s="14" t="n"/>
       <c r="B16" s="14" t="n"/>
       <c r="C16" s="15" t="n"/>
-      <c r="D16" s="17" t="n"/>
-      <c r="E16" s="17" t="n"/>
+      <c r="D16" s="27" t="n"/>
+      <c r="E16" s="27" t="n"/>
       <c r="F16" s="14" t="n"/>
       <c r="G16" s="14">
         <f>IF(OR(F16="Pago",E16="",E16&gt;=TODAY()),0,TODAY()-E16)</f>
@@ -2245,7 +2864,7 @@
         <f>IF(F16="Pago","Pago",IF(G16=0,"A vencer",IF(G16&lt;=30,"1-30",IF(G16&lt;=60,"31-60",IF(G16&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I16" s="18">
+      <c r="I16" s="28">
         <f>IF(F16="Pago",1,IF(G16=0,0.97,IF(G16&lt;=30,0.9,IF(G16&lt;=60,0.72,IF(G16&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -2263,8 +2882,8 @@
       <c r="A17" s="14" t="n"/>
       <c r="B17" s="14" t="n"/>
       <c r="C17" s="15" t="n"/>
-      <c r="D17" s="17" t="n"/>
-      <c r="E17" s="17" t="n"/>
+      <c r="D17" s="27" t="n"/>
+      <c r="E17" s="27" t="n"/>
       <c r="F17" s="14" t="n"/>
       <c r="G17" s="14">
         <f>IF(OR(F17="Pago",E17="",E17&gt;=TODAY()),0,TODAY()-E17)</f>
@@ -2274,7 +2893,7 @@
         <f>IF(F17="Pago","Pago",IF(G17=0,"A vencer",IF(G17&lt;=30,"1-30",IF(G17&lt;=60,"31-60",IF(G17&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I17" s="18">
+      <c r="I17" s="28">
         <f>IF(F17="Pago",1,IF(G17=0,0.97,IF(G17&lt;=30,0.9,IF(G17&lt;=60,0.72,IF(G17&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -2292,8 +2911,8 @@
       <c r="A18" s="14" t="n"/>
       <c r="B18" s="14" t="n"/>
       <c r="C18" s="15" t="n"/>
-      <c r="D18" s="17" t="n"/>
-      <c r="E18" s="17" t="n"/>
+      <c r="D18" s="27" t="n"/>
+      <c r="E18" s="27" t="n"/>
       <c r="F18" s="14" t="n"/>
       <c r="G18" s="14">
         <f>IF(OR(F18="Pago",E18="",E18&gt;=TODAY()),0,TODAY()-E18)</f>
@@ -2303,7 +2922,7 @@
         <f>IF(F18="Pago","Pago",IF(G18=0,"A vencer",IF(G18&lt;=30,"1-30",IF(G18&lt;=60,"31-60",IF(G18&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I18" s="18">
+      <c r="I18" s="28">
         <f>IF(F18="Pago",1,IF(G18=0,0.97,IF(G18&lt;=30,0.9,IF(G18&lt;=60,0.72,IF(G18&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -2321,8 +2940,8 @@
       <c r="A19" s="14" t="n"/>
       <c r="B19" s="14" t="n"/>
       <c r="C19" s="15" t="n"/>
-      <c r="D19" s="17" t="n"/>
-      <c r="E19" s="17" t="n"/>
+      <c r="D19" s="27" t="n"/>
+      <c r="E19" s="27" t="n"/>
       <c r="F19" s="14" t="n"/>
       <c r="G19" s="14">
         <f>IF(OR(F19="Pago",E19="",E19&gt;=TODAY()),0,TODAY()-E19)</f>
@@ -2332,7 +2951,7 @@
         <f>IF(F19="Pago","Pago",IF(G19=0,"A vencer",IF(G19&lt;=30,"1-30",IF(G19&lt;=60,"31-60",IF(G19&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I19" s="18">
+      <c r="I19" s="28">
         <f>IF(F19="Pago",1,IF(G19=0,0.97,IF(G19&lt;=30,0.9,IF(G19&lt;=60,0.72,IF(G19&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -2350,8 +2969,8 @@
       <c r="A20" s="14" t="n"/>
       <c r="B20" s="14" t="n"/>
       <c r="C20" s="15" t="n"/>
-      <c r="D20" s="17" t="n"/>
-      <c r="E20" s="17" t="n"/>
+      <c r="D20" s="27" t="n"/>
+      <c r="E20" s="27" t="n"/>
       <c r="F20" s="14" t="n"/>
       <c r="G20" s="14">
         <f>IF(OR(F20="Pago",E20="",E20&gt;=TODAY()),0,TODAY()-E20)</f>
@@ -2361,7 +2980,7 @@
         <f>IF(F20="Pago","Pago",IF(G20=0,"A vencer",IF(G20&lt;=30,"1-30",IF(G20&lt;=60,"31-60",IF(G20&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I20" s="18">
+      <c r="I20" s="28">
         <f>IF(F20="Pago",1,IF(G20=0,0.97,IF(G20&lt;=30,0.9,IF(G20&lt;=60,0.72,IF(G20&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -2379,8 +2998,8 @@
       <c r="A21" s="14" t="n"/>
       <c r="B21" s="14" t="n"/>
       <c r="C21" s="15" t="n"/>
-      <c r="D21" s="17" t="n"/>
-      <c r="E21" s="17" t="n"/>
+      <c r="D21" s="27" t="n"/>
+      <c r="E21" s="27" t="n"/>
       <c r="F21" s="14" t="n"/>
       <c r="G21" s="14">
         <f>IF(OR(F21="Pago",E21="",E21&gt;=TODAY()),0,TODAY()-E21)</f>
@@ -2390,7 +3009,7 @@
         <f>IF(F21="Pago","Pago",IF(G21=0,"A vencer",IF(G21&lt;=30,"1-30",IF(G21&lt;=60,"31-60",IF(G21&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I21" s="18">
+      <c r="I21" s="28">
         <f>IF(F21="Pago",1,IF(G21=0,0.97,IF(G21&lt;=30,0.9,IF(G21&lt;=60,0.72,IF(G21&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -2408,8 +3027,8 @@
       <c r="A22" s="14" t="n"/>
       <c r="B22" s="14" t="n"/>
       <c r="C22" s="15" t="n"/>
-      <c r="D22" s="17" t="n"/>
-      <c r="E22" s="17" t="n"/>
+      <c r="D22" s="27" t="n"/>
+      <c r="E22" s="27" t="n"/>
       <c r="F22" s="14" t="n"/>
       <c r="G22" s="14">
         <f>IF(OR(F22="Pago",E22="",E22&gt;=TODAY()),0,TODAY()-E22)</f>
@@ -2419,7 +3038,7 @@
         <f>IF(F22="Pago","Pago",IF(G22=0,"A vencer",IF(G22&lt;=30,"1-30",IF(G22&lt;=60,"31-60",IF(G22&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I22" s="18">
+      <c r="I22" s="28">
         <f>IF(F22="Pago",1,IF(G22=0,0.97,IF(G22&lt;=30,0.9,IF(G22&lt;=60,0.72,IF(G22&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -2437,8 +3056,8 @@
       <c r="A23" s="14" t="n"/>
       <c r="B23" s="14" t="n"/>
       <c r="C23" s="15" t="n"/>
-      <c r="D23" s="17" t="n"/>
-      <c r="E23" s="17" t="n"/>
+      <c r="D23" s="27" t="n"/>
+      <c r="E23" s="27" t="n"/>
       <c r="F23" s="14" t="n"/>
       <c r="G23" s="14">
         <f>IF(OR(F23="Pago",E23="",E23&gt;=TODAY()),0,TODAY()-E23)</f>
@@ -2448,7 +3067,7 @@
         <f>IF(F23="Pago","Pago",IF(G23=0,"A vencer",IF(G23&lt;=30,"1-30",IF(G23&lt;=60,"31-60",IF(G23&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I23" s="18">
+      <c r="I23" s="28">
         <f>IF(F23="Pago",1,IF(G23=0,0.97,IF(G23&lt;=30,0.9,IF(G23&lt;=60,0.72,IF(G23&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -2466,8 +3085,8 @@
       <c r="A24" s="14" t="n"/>
       <c r="B24" s="14" t="n"/>
       <c r="C24" s="15" t="n"/>
-      <c r="D24" s="17" t="n"/>
-      <c r="E24" s="17" t="n"/>
+      <c r="D24" s="27" t="n"/>
+      <c r="E24" s="27" t="n"/>
       <c r="F24" s="14" t="n"/>
       <c r="G24" s="14">
         <f>IF(OR(F24="Pago",E24="",E24&gt;=TODAY()),0,TODAY()-E24)</f>
@@ -2477,7 +3096,7 @@
         <f>IF(F24="Pago","Pago",IF(G24=0,"A vencer",IF(G24&lt;=30,"1-30",IF(G24&lt;=60,"31-60",IF(G24&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I24" s="18">
+      <c r="I24" s="28">
         <f>IF(F24="Pago",1,IF(G24=0,0.97,IF(G24&lt;=30,0.9,IF(G24&lt;=60,0.72,IF(G24&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -2495,8 +3114,8 @@
       <c r="A25" s="14" t="n"/>
       <c r="B25" s="14" t="n"/>
       <c r="C25" s="15" t="n"/>
-      <c r="D25" s="17" t="n"/>
-      <c r="E25" s="17" t="n"/>
+      <c r="D25" s="27" t="n"/>
+      <c r="E25" s="27" t="n"/>
       <c r="F25" s="14" t="n"/>
       <c r="G25" s="14">
         <f>IF(OR(F25="Pago",E25="",E25&gt;=TODAY()),0,TODAY()-E25)</f>
@@ -2506,7 +3125,7 @@
         <f>IF(F25="Pago","Pago",IF(G25=0,"A vencer",IF(G25&lt;=30,"1-30",IF(G25&lt;=60,"31-60",IF(G25&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I25" s="18">
+      <c r="I25" s="28">
         <f>IF(F25="Pago",1,IF(G25=0,0.97,IF(G25&lt;=30,0.9,IF(G25&lt;=60,0.72,IF(G25&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -2524,8 +3143,8 @@
       <c r="A26" s="14" t="n"/>
       <c r="B26" s="14" t="n"/>
       <c r="C26" s="15" t="n"/>
-      <c r="D26" s="17" t="n"/>
-      <c r="E26" s="17" t="n"/>
+      <c r="D26" s="27" t="n"/>
+      <c r="E26" s="27" t="n"/>
       <c r="F26" s="14" t="n"/>
       <c r="G26" s="14">
         <f>IF(OR(F26="Pago",E26="",E26&gt;=TODAY()),0,TODAY()-E26)</f>
@@ -2535,7 +3154,7 @@
         <f>IF(F26="Pago","Pago",IF(G26=0,"A vencer",IF(G26&lt;=30,"1-30",IF(G26&lt;=60,"31-60",IF(G26&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I26" s="18">
+      <c r="I26" s="28">
         <f>IF(F26="Pago",1,IF(G26=0,0.97,IF(G26&lt;=30,0.9,IF(G26&lt;=60,0.72,IF(G26&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -2553,8 +3172,8 @@
       <c r="A27" s="14" t="n"/>
       <c r="B27" s="14" t="n"/>
       <c r="C27" s="15" t="n"/>
-      <c r="D27" s="17" t="n"/>
-      <c r="E27" s="17" t="n"/>
+      <c r="D27" s="27" t="n"/>
+      <c r="E27" s="27" t="n"/>
       <c r="F27" s="14" t="n"/>
       <c r="G27" s="14">
         <f>IF(OR(F27="Pago",E27="",E27&gt;=TODAY()),0,TODAY()-E27)</f>
@@ -2564,7 +3183,7 @@
         <f>IF(F27="Pago","Pago",IF(G27=0,"A vencer",IF(G27&lt;=30,"1-30",IF(G27&lt;=60,"31-60",IF(G27&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I27" s="18">
+      <c r="I27" s="28">
         <f>IF(F27="Pago",1,IF(G27=0,0.97,IF(G27&lt;=30,0.9,IF(G27&lt;=60,0.72,IF(G27&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -2582,8 +3201,8 @@
       <c r="A28" s="14" t="n"/>
       <c r="B28" s="14" t="n"/>
       <c r="C28" s="15" t="n"/>
-      <c r="D28" s="17" t="n"/>
-      <c r="E28" s="17" t="n"/>
+      <c r="D28" s="27" t="n"/>
+      <c r="E28" s="27" t="n"/>
       <c r="F28" s="14" t="n"/>
       <c r="G28" s="14">
         <f>IF(OR(F28="Pago",E28="",E28&gt;=TODAY()),0,TODAY()-E28)</f>
@@ -2593,7 +3212,7 @@
         <f>IF(F28="Pago","Pago",IF(G28=0,"A vencer",IF(G28&lt;=30,"1-30",IF(G28&lt;=60,"31-60",IF(G28&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I28" s="18">
+      <c r="I28" s="28">
         <f>IF(F28="Pago",1,IF(G28=0,0.97,IF(G28&lt;=30,0.9,IF(G28&lt;=60,0.72,IF(G28&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -2611,8 +3230,8 @@
       <c r="A29" s="14" t="n"/>
       <c r="B29" s="14" t="n"/>
       <c r="C29" s="15" t="n"/>
-      <c r="D29" s="17" t="n"/>
-      <c r="E29" s="17" t="n"/>
+      <c r="D29" s="27" t="n"/>
+      <c r="E29" s="27" t="n"/>
       <c r="F29" s="14" t="n"/>
       <c r="G29" s="14">
         <f>IF(OR(F29="Pago",E29="",E29&gt;=TODAY()),0,TODAY()-E29)</f>
@@ -2622,7 +3241,7 @@
         <f>IF(F29="Pago","Pago",IF(G29=0,"A vencer",IF(G29&lt;=30,"1-30",IF(G29&lt;=60,"31-60",IF(G29&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I29" s="18">
+      <c r="I29" s="28">
         <f>IF(F29="Pago",1,IF(G29=0,0.97,IF(G29&lt;=30,0.9,IF(G29&lt;=60,0.72,IF(G29&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -2640,8 +3259,8 @@
       <c r="A30" s="14" t="n"/>
       <c r="B30" s="14" t="n"/>
       <c r="C30" s="15" t="n"/>
-      <c r="D30" s="17" t="n"/>
-      <c r="E30" s="17" t="n"/>
+      <c r="D30" s="27" t="n"/>
+      <c r="E30" s="27" t="n"/>
       <c r="F30" s="14" t="n"/>
       <c r="G30" s="14">
         <f>IF(OR(F30="Pago",E30="",E30&gt;=TODAY()),0,TODAY()-E30)</f>
@@ -2651,7 +3270,7 @@
         <f>IF(F30="Pago","Pago",IF(G30=0,"A vencer",IF(G30&lt;=30,"1-30",IF(G30&lt;=60,"31-60",IF(G30&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I30" s="18">
+      <c r="I30" s="28">
         <f>IF(F30="Pago",1,IF(G30=0,0.97,IF(G30&lt;=30,0.9,IF(G30&lt;=60,0.72,IF(G30&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -2669,8 +3288,8 @@
       <c r="A31" s="14" t="n"/>
       <c r="B31" s="14" t="n"/>
       <c r="C31" s="15" t="n"/>
-      <c r="D31" s="17" t="n"/>
-      <c r="E31" s="17" t="n"/>
+      <c r="D31" s="27" t="n"/>
+      <c r="E31" s="27" t="n"/>
       <c r="F31" s="14" t="n"/>
       <c r="G31" s="14">
         <f>IF(OR(F31="Pago",E31="",E31&gt;=TODAY()),0,TODAY()-E31)</f>
@@ -2680,7 +3299,7 @@
         <f>IF(F31="Pago","Pago",IF(G31=0,"A vencer",IF(G31&lt;=30,"1-30",IF(G31&lt;=60,"31-60",IF(G31&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I31" s="18">
+      <c r="I31" s="28">
         <f>IF(F31="Pago",1,IF(G31=0,0.97,IF(G31&lt;=30,0.9,IF(G31&lt;=60,0.72,IF(G31&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -2698,8 +3317,8 @@
       <c r="A32" s="14" t="n"/>
       <c r="B32" s="14" t="n"/>
       <c r="C32" s="15" t="n"/>
-      <c r="D32" s="17" t="n"/>
-      <c r="E32" s="17" t="n"/>
+      <c r="D32" s="27" t="n"/>
+      <c r="E32" s="27" t="n"/>
       <c r="F32" s="14" t="n"/>
       <c r="G32" s="14">
         <f>IF(OR(F32="Pago",E32="",E32&gt;=TODAY()),0,TODAY()-E32)</f>
@@ -2709,7 +3328,7 @@
         <f>IF(F32="Pago","Pago",IF(G32=0,"A vencer",IF(G32&lt;=30,"1-30",IF(G32&lt;=60,"31-60",IF(G32&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I32" s="18">
+      <c r="I32" s="28">
         <f>IF(F32="Pago",1,IF(G32=0,0.97,IF(G32&lt;=30,0.9,IF(G32&lt;=60,0.72,IF(G32&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -2727,8 +3346,8 @@
       <c r="A33" s="14" t="n"/>
       <c r="B33" s="14" t="n"/>
       <c r="C33" s="15" t="n"/>
-      <c r="D33" s="17" t="n"/>
-      <c r="E33" s="17" t="n"/>
+      <c r="D33" s="27" t="n"/>
+      <c r="E33" s="27" t="n"/>
       <c r="F33" s="14" t="n"/>
       <c r="G33" s="14">
         <f>IF(OR(F33="Pago",E33="",E33&gt;=TODAY()),0,TODAY()-E33)</f>
@@ -2738,7 +3357,7 @@
         <f>IF(F33="Pago","Pago",IF(G33=0,"A vencer",IF(G33&lt;=30,"1-30",IF(G33&lt;=60,"31-60",IF(G33&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I33" s="18">
+      <c r="I33" s="28">
         <f>IF(F33="Pago",1,IF(G33=0,0.97,IF(G33&lt;=30,0.9,IF(G33&lt;=60,0.72,IF(G33&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -2756,8 +3375,8 @@
       <c r="A34" s="14" t="n"/>
       <c r="B34" s="14" t="n"/>
       <c r="C34" s="15" t="n"/>
-      <c r="D34" s="17" t="n"/>
-      <c r="E34" s="17" t="n"/>
+      <c r="D34" s="27" t="n"/>
+      <c r="E34" s="27" t="n"/>
       <c r="F34" s="14" t="n"/>
       <c r="G34" s="14">
         <f>IF(OR(F34="Pago",E34="",E34&gt;=TODAY()),0,TODAY()-E34)</f>
@@ -2767,7 +3386,7 @@
         <f>IF(F34="Pago","Pago",IF(G34=0,"A vencer",IF(G34&lt;=30,"1-30",IF(G34&lt;=60,"31-60",IF(G34&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I34" s="18">
+      <c r="I34" s="28">
         <f>IF(F34="Pago",1,IF(G34=0,0.97,IF(G34&lt;=30,0.9,IF(G34&lt;=60,0.72,IF(G34&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -2785,8 +3404,8 @@
       <c r="A35" s="14" t="n"/>
       <c r="B35" s="14" t="n"/>
       <c r="C35" s="15" t="n"/>
-      <c r="D35" s="17" t="n"/>
-      <c r="E35" s="17" t="n"/>
+      <c r="D35" s="27" t="n"/>
+      <c r="E35" s="27" t="n"/>
       <c r="F35" s="14" t="n"/>
       <c r="G35" s="14">
         <f>IF(OR(F35="Pago",E35="",E35&gt;=TODAY()),0,TODAY()-E35)</f>
@@ -2796,7 +3415,7 @@
         <f>IF(F35="Pago","Pago",IF(G35=0,"A vencer",IF(G35&lt;=30,"1-30",IF(G35&lt;=60,"31-60",IF(G35&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I35" s="18">
+      <c r="I35" s="28">
         <f>IF(F35="Pago",1,IF(G35=0,0.97,IF(G35&lt;=30,0.9,IF(G35&lt;=60,0.72,IF(G35&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -2814,8 +3433,8 @@
       <c r="A36" s="14" t="n"/>
       <c r="B36" s="14" t="n"/>
       <c r="C36" s="15" t="n"/>
-      <c r="D36" s="17" t="n"/>
-      <c r="E36" s="17" t="n"/>
+      <c r="D36" s="27" t="n"/>
+      <c r="E36" s="27" t="n"/>
       <c r="F36" s="14" t="n"/>
       <c r="G36" s="14">
         <f>IF(OR(F36="Pago",E36="",E36&gt;=TODAY()),0,TODAY()-E36)</f>
@@ -2825,7 +3444,7 @@
         <f>IF(F36="Pago","Pago",IF(G36=0,"A vencer",IF(G36&lt;=30,"1-30",IF(G36&lt;=60,"31-60",IF(G36&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I36" s="18">
+      <c r="I36" s="28">
         <f>IF(F36="Pago",1,IF(G36=0,0.97,IF(G36&lt;=30,0.9,IF(G36&lt;=60,0.72,IF(G36&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -2843,8 +3462,8 @@
       <c r="A37" s="14" t="n"/>
       <c r="B37" s="14" t="n"/>
       <c r="C37" s="15" t="n"/>
-      <c r="D37" s="17" t="n"/>
-      <c r="E37" s="17" t="n"/>
+      <c r="D37" s="27" t="n"/>
+      <c r="E37" s="27" t="n"/>
       <c r="F37" s="14" t="n"/>
       <c r="G37" s="14">
         <f>IF(OR(F37="Pago",E37="",E37&gt;=TODAY()),0,TODAY()-E37)</f>
@@ -2854,7 +3473,7 @@
         <f>IF(F37="Pago","Pago",IF(G37=0,"A vencer",IF(G37&lt;=30,"1-30",IF(G37&lt;=60,"31-60",IF(G37&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I37" s="18">
+      <c r="I37" s="28">
         <f>IF(F37="Pago",1,IF(G37=0,0.97,IF(G37&lt;=30,0.9,IF(G37&lt;=60,0.72,IF(G37&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -2872,8 +3491,8 @@
       <c r="A38" s="14" t="n"/>
       <c r="B38" s="14" t="n"/>
       <c r="C38" s="15" t="n"/>
-      <c r="D38" s="17" t="n"/>
-      <c r="E38" s="17" t="n"/>
+      <c r="D38" s="27" t="n"/>
+      <c r="E38" s="27" t="n"/>
       <c r="F38" s="14" t="n"/>
       <c r="G38" s="14">
         <f>IF(OR(F38="Pago",E38="",E38&gt;=TODAY()),0,TODAY()-E38)</f>
@@ -2883,7 +3502,7 @@
         <f>IF(F38="Pago","Pago",IF(G38=0,"A vencer",IF(G38&lt;=30,"1-30",IF(G38&lt;=60,"31-60",IF(G38&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I38" s="18">
+      <c r="I38" s="28">
         <f>IF(F38="Pago",1,IF(G38=0,0.97,IF(G38&lt;=30,0.9,IF(G38&lt;=60,0.72,IF(G38&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -2901,8 +3520,8 @@
       <c r="A39" s="14" t="n"/>
       <c r="B39" s="14" t="n"/>
       <c r="C39" s="15" t="n"/>
-      <c r="D39" s="17" t="n"/>
-      <c r="E39" s="17" t="n"/>
+      <c r="D39" s="27" t="n"/>
+      <c r="E39" s="27" t="n"/>
       <c r="F39" s="14" t="n"/>
       <c r="G39" s="14">
         <f>IF(OR(F39="Pago",E39="",E39&gt;=TODAY()),0,TODAY()-E39)</f>
@@ -2912,7 +3531,7 @@
         <f>IF(F39="Pago","Pago",IF(G39=0,"A vencer",IF(G39&lt;=30,"1-30",IF(G39&lt;=60,"31-60",IF(G39&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I39" s="18">
+      <c r="I39" s="28">
         <f>IF(F39="Pago",1,IF(G39=0,0.97,IF(G39&lt;=30,0.9,IF(G39&lt;=60,0.72,IF(G39&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -2930,8 +3549,8 @@
       <c r="A40" s="14" t="n"/>
       <c r="B40" s="14" t="n"/>
       <c r="C40" s="15" t="n"/>
-      <c r="D40" s="17" t="n"/>
-      <c r="E40" s="17" t="n"/>
+      <c r="D40" s="27" t="n"/>
+      <c r="E40" s="27" t="n"/>
       <c r="F40" s="14" t="n"/>
       <c r="G40" s="14">
         <f>IF(OR(F40="Pago",E40="",E40&gt;=TODAY()),0,TODAY()-E40)</f>
@@ -2941,7 +3560,7 @@
         <f>IF(F40="Pago","Pago",IF(G40=0,"A vencer",IF(G40&lt;=30,"1-30",IF(G40&lt;=60,"31-60",IF(G40&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I40" s="18">
+      <c r="I40" s="28">
         <f>IF(F40="Pago",1,IF(G40=0,0.97,IF(G40&lt;=30,0.9,IF(G40&lt;=60,0.72,IF(G40&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -2959,8 +3578,8 @@
       <c r="A41" s="14" t="n"/>
       <c r="B41" s="14" t="n"/>
       <c r="C41" s="15" t="n"/>
-      <c r="D41" s="17" t="n"/>
-      <c r="E41" s="17" t="n"/>
+      <c r="D41" s="27" t="n"/>
+      <c r="E41" s="27" t="n"/>
       <c r="F41" s="14" t="n"/>
       <c r="G41" s="14">
         <f>IF(OR(F41="Pago",E41="",E41&gt;=TODAY()),0,TODAY()-E41)</f>
@@ -2970,7 +3589,7 @@
         <f>IF(F41="Pago","Pago",IF(G41=0,"A vencer",IF(G41&lt;=30,"1-30",IF(G41&lt;=60,"31-60",IF(G41&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I41" s="18">
+      <c r="I41" s="28">
         <f>IF(F41="Pago",1,IF(G41=0,0.97,IF(G41&lt;=30,0.9,IF(G41&lt;=60,0.72,IF(G41&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -2988,8 +3607,8 @@
       <c r="A42" s="14" t="n"/>
       <c r="B42" s="14" t="n"/>
       <c r="C42" s="15" t="n"/>
-      <c r="D42" s="17" t="n"/>
-      <c r="E42" s="17" t="n"/>
+      <c r="D42" s="27" t="n"/>
+      <c r="E42" s="27" t="n"/>
       <c r="F42" s="14" t="n"/>
       <c r="G42" s="14">
         <f>IF(OR(F42="Pago",E42="",E42&gt;=TODAY()),0,TODAY()-E42)</f>
@@ -2999,7 +3618,7 @@
         <f>IF(F42="Pago","Pago",IF(G42=0,"A vencer",IF(G42&lt;=30,"1-30",IF(G42&lt;=60,"31-60",IF(G42&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I42" s="18">
+      <c r="I42" s="28">
         <f>IF(F42="Pago",1,IF(G42=0,0.97,IF(G42&lt;=30,0.9,IF(G42&lt;=60,0.72,IF(G42&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -3017,8 +3636,8 @@
       <c r="A43" s="14" t="n"/>
       <c r="B43" s="14" t="n"/>
       <c r="C43" s="15" t="n"/>
-      <c r="D43" s="17" t="n"/>
-      <c r="E43" s="17" t="n"/>
+      <c r="D43" s="27" t="n"/>
+      <c r="E43" s="27" t="n"/>
       <c r="F43" s="14" t="n"/>
       <c r="G43" s="14">
         <f>IF(OR(F43="Pago",E43="",E43&gt;=TODAY()),0,TODAY()-E43)</f>
@@ -3028,7 +3647,7 @@
         <f>IF(F43="Pago","Pago",IF(G43=0,"A vencer",IF(G43&lt;=30,"1-30",IF(G43&lt;=60,"31-60",IF(G43&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I43" s="18">
+      <c r="I43" s="28">
         <f>IF(F43="Pago",1,IF(G43=0,0.97,IF(G43&lt;=30,0.9,IF(G43&lt;=60,0.72,IF(G43&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -3046,8 +3665,8 @@
       <c r="A44" s="14" t="n"/>
       <c r="B44" s="14" t="n"/>
       <c r="C44" s="15" t="n"/>
-      <c r="D44" s="17" t="n"/>
-      <c r="E44" s="17" t="n"/>
+      <c r="D44" s="27" t="n"/>
+      <c r="E44" s="27" t="n"/>
       <c r="F44" s="14" t="n"/>
       <c r="G44" s="14">
         <f>IF(OR(F44="Pago",E44="",E44&gt;=TODAY()),0,TODAY()-E44)</f>
@@ -3057,7 +3676,7 @@
         <f>IF(F44="Pago","Pago",IF(G44=0,"A vencer",IF(G44&lt;=30,"1-30",IF(G44&lt;=60,"31-60",IF(G44&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I44" s="18">
+      <c r="I44" s="28">
         <f>IF(F44="Pago",1,IF(G44=0,0.97,IF(G44&lt;=30,0.9,IF(G44&lt;=60,0.72,IF(G44&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -3075,8 +3694,8 @@
       <c r="A45" s="14" t="n"/>
       <c r="B45" s="14" t="n"/>
       <c r="C45" s="15" t="n"/>
-      <c r="D45" s="17" t="n"/>
-      <c r="E45" s="17" t="n"/>
+      <c r="D45" s="27" t="n"/>
+      <c r="E45" s="27" t="n"/>
       <c r="F45" s="14" t="n"/>
       <c r="G45" s="14">
         <f>IF(OR(F45="Pago",E45="",E45&gt;=TODAY()),0,TODAY()-E45)</f>
@@ -3086,7 +3705,7 @@
         <f>IF(F45="Pago","Pago",IF(G45=0,"A vencer",IF(G45&lt;=30,"1-30",IF(G45&lt;=60,"31-60",IF(G45&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I45" s="18">
+      <c r="I45" s="28">
         <f>IF(F45="Pago",1,IF(G45=0,0.97,IF(G45&lt;=30,0.9,IF(G45&lt;=60,0.72,IF(G45&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -3104,8 +3723,8 @@
       <c r="A46" s="14" t="n"/>
       <c r="B46" s="14" t="n"/>
       <c r="C46" s="15" t="n"/>
-      <c r="D46" s="17" t="n"/>
-      <c r="E46" s="17" t="n"/>
+      <c r="D46" s="27" t="n"/>
+      <c r="E46" s="27" t="n"/>
       <c r="F46" s="14" t="n"/>
       <c r="G46" s="14">
         <f>IF(OR(F46="Pago",E46="",E46&gt;=TODAY()),0,TODAY()-E46)</f>
@@ -3115,7 +3734,7 @@
         <f>IF(F46="Pago","Pago",IF(G46=0,"A vencer",IF(G46&lt;=30,"1-30",IF(G46&lt;=60,"31-60",IF(G46&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I46" s="18">
+      <c r="I46" s="28">
         <f>IF(F46="Pago",1,IF(G46=0,0.97,IF(G46&lt;=30,0.9,IF(G46&lt;=60,0.72,IF(G46&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -3133,8 +3752,8 @@
       <c r="A47" s="14" t="n"/>
       <c r="B47" s="14" t="n"/>
       <c r="C47" s="15" t="n"/>
-      <c r="D47" s="17" t="n"/>
-      <c r="E47" s="17" t="n"/>
+      <c r="D47" s="27" t="n"/>
+      <c r="E47" s="27" t="n"/>
       <c r="F47" s="14" t="n"/>
       <c r="G47" s="14">
         <f>IF(OR(F47="Pago",E47="",E47&gt;=TODAY()),0,TODAY()-E47)</f>
@@ -3144,7 +3763,7 @@
         <f>IF(F47="Pago","Pago",IF(G47=0,"A vencer",IF(G47&lt;=30,"1-30",IF(G47&lt;=60,"31-60",IF(G47&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I47" s="18">
+      <c r="I47" s="28">
         <f>IF(F47="Pago",1,IF(G47=0,0.97,IF(G47&lt;=30,0.9,IF(G47&lt;=60,0.72,IF(G47&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -3162,8 +3781,8 @@
       <c r="A48" s="14" t="n"/>
       <c r="B48" s="14" t="n"/>
       <c r="C48" s="15" t="n"/>
-      <c r="D48" s="17" t="n"/>
-      <c r="E48" s="17" t="n"/>
+      <c r="D48" s="27" t="n"/>
+      <c r="E48" s="27" t="n"/>
       <c r="F48" s="14" t="n"/>
       <c r="G48" s="14">
         <f>IF(OR(F48="Pago",E48="",E48&gt;=TODAY()),0,TODAY()-E48)</f>
@@ -3173,7 +3792,7 @@
         <f>IF(F48="Pago","Pago",IF(G48=0,"A vencer",IF(G48&lt;=30,"1-30",IF(G48&lt;=60,"31-60",IF(G48&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I48" s="18">
+      <c r="I48" s="28">
         <f>IF(F48="Pago",1,IF(G48=0,0.97,IF(G48&lt;=30,0.9,IF(G48&lt;=60,0.72,IF(G48&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -3191,8 +3810,8 @@
       <c r="A49" s="14" t="n"/>
       <c r="B49" s="14" t="n"/>
       <c r="C49" s="15" t="n"/>
-      <c r="D49" s="17" t="n"/>
-      <c r="E49" s="17" t="n"/>
+      <c r="D49" s="27" t="n"/>
+      <c r="E49" s="27" t="n"/>
       <c r="F49" s="14" t="n"/>
       <c r="G49" s="14">
         <f>IF(OR(F49="Pago",E49="",E49&gt;=TODAY()),0,TODAY()-E49)</f>
@@ -3202,7 +3821,7 @@
         <f>IF(F49="Pago","Pago",IF(G49=0,"A vencer",IF(G49&lt;=30,"1-30",IF(G49&lt;=60,"31-60",IF(G49&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I49" s="18">
+      <c r="I49" s="28">
         <f>IF(F49="Pago",1,IF(G49=0,0.97,IF(G49&lt;=30,0.9,IF(G49&lt;=60,0.72,IF(G49&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -3220,8 +3839,8 @@
       <c r="A50" s="14" t="n"/>
       <c r="B50" s="14" t="n"/>
       <c r="C50" s="15" t="n"/>
-      <c r="D50" s="17" t="n"/>
-      <c r="E50" s="17" t="n"/>
+      <c r="D50" s="27" t="n"/>
+      <c r="E50" s="27" t="n"/>
       <c r="F50" s="14" t="n"/>
       <c r="G50" s="14">
         <f>IF(OR(F50="Pago",E50="",E50&gt;=TODAY()),0,TODAY()-E50)</f>
@@ -3231,7 +3850,7 @@
         <f>IF(F50="Pago","Pago",IF(G50=0,"A vencer",IF(G50&lt;=30,"1-30",IF(G50&lt;=60,"31-60",IF(G50&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I50" s="18">
+      <c r="I50" s="28">
         <f>IF(F50="Pago",1,IF(G50=0,0.97,IF(G50&lt;=30,0.9,IF(G50&lt;=60,0.72,IF(G50&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -3249,8 +3868,8 @@
       <c r="A51" s="14" t="n"/>
       <c r="B51" s="14" t="n"/>
       <c r="C51" s="15" t="n"/>
-      <c r="D51" s="17" t="n"/>
-      <c r="E51" s="17" t="n"/>
+      <c r="D51" s="27" t="n"/>
+      <c r="E51" s="27" t="n"/>
       <c r="F51" s="14" t="n"/>
       <c r="G51" s="14">
         <f>IF(OR(F51="Pago",E51="",E51&gt;=TODAY()),0,TODAY()-E51)</f>
@@ -3260,7 +3879,7 @@
         <f>IF(F51="Pago","Pago",IF(G51=0,"A vencer",IF(G51&lt;=30,"1-30",IF(G51&lt;=60,"31-60",IF(G51&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I51" s="18">
+      <c r="I51" s="28">
         <f>IF(F51="Pago",1,IF(G51=0,0.97,IF(G51&lt;=30,0.9,IF(G51&lt;=60,0.72,IF(G51&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -3278,8 +3897,8 @@
       <c r="A52" s="14" t="n"/>
       <c r="B52" s="14" t="n"/>
       <c r="C52" s="15" t="n"/>
-      <c r="D52" s="17" t="n"/>
-      <c r="E52" s="17" t="n"/>
+      <c r="D52" s="27" t="n"/>
+      <c r="E52" s="27" t="n"/>
       <c r="F52" s="14" t="n"/>
       <c r="G52" s="14">
         <f>IF(OR(F52="Pago",E52="",E52&gt;=TODAY()),0,TODAY()-E52)</f>
@@ -3289,7 +3908,7 @@
         <f>IF(F52="Pago","Pago",IF(G52=0,"A vencer",IF(G52&lt;=30,"1-30",IF(G52&lt;=60,"31-60",IF(G52&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I52" s="18">
+      <c r="I52" s="28">
         <f>IF(F52="Pago",1,IF(G52=0,0.97,IF(G52&lt;=30,0.9,IF(G52&lt;=60,0.72,IF(G52&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -3307,8 +3926,8 @@
       <c r="A53" s="14" t="n"/>
       <c r="B53" s="14" t="n"/>
       <c r="C53" s="15" t="n"/>
-      <c r="D53" s="17" t="n"/>
-      <c r="E53" s="17" t="n"/>
+      <c r="D53" s="27" t="n"/>
+      <c r="E53" s="27" t="n"/>
       <c r="F53" s="14" t="n"/>
       <c r="G53" s="14">
         <f>IF(OR(F53="Pago",E53="",E53&gt;=TODAY()),0,TODAY()-E53)</f>
@@ -3318,7 +3937,7 @@
         <f>IF(F53="Pago","Pago",IF(G53=0,"A vencer",IF(G53&lt;=30,"1-30",IF(G53&lt;=60,"31-60",IF(G53&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I53" s="18">
+      <c r="I53" s="28">
         <f>IF(F53="Pago",1,IF(G53=0,0.97,IF(G53&lt;=30,0.9,IF(G53&lt;=60,0.72,IF(G53&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -3336,8 +3955,8 @@
       <c r="A54" s="14" t="n"/>
       <c r="B54" s="14" t="n"/>
       <c r="C54" s="15" t="n"/>
-      <c r="D54" s="17" t="n"/>
-      <c r="E54" s="17" t="n"/>
+      <c r="D54" s="27" t="n"/>
+      <c r="E54" s="27" t="n"/>
       <c r="F54" s="14" t="n"/>
       <c r="G54" s="14">
         <f>IF(OR(F54="Pago",E54="",E54&gt;=TODAY()),0,TODAY()-E54)</f>
@@ -3347,7 +3966,7 @@
         <f>IF(F54="Pago","Pago",IF(G54=0,"A vencer",IF(G54&lt;=30,"1-30",IF(G54&lt;=60,"31-60",IF(G54&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I54" s="18">
+      <c r="I54" s="28">
         <f>IF(F54="Pago",1,IF(G54=0,0.97,IF(G54&lt;=30,0.9,IF(G54&lt;=60,0.72,IF(G54&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -3365,8 +3984,8 @@
       <c r="A55" s="14" t="n"/>
       <c r="B55" s="14" t="n"/>
       <c r="C55" s="15" t="n"/>
-      <c r="D55" s="17" t="n"/>
-      <c r="E55" s="17" t="n"/>
+      <c r="D55" s="27" t="n"/>
+      <c r="E55" s="27" t="n"/>
       <c r="F55" s="14" t="n"/>
       <c r="G55" s="14">
         <f>IF(OR(F55="Pago",E55="",E55&gt;=TODAY()),0,TODAY()-E55)</f>
@@ -3376,7 +3995,7 @@
         <f>IF(F55="Pago","Pago",IF(G55=0,"A vencer",IF(G55&lt;=30,"1-30",IF(G55&lt;=60,"31-60",IF(G55&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I55" s="18">
+      <c r="I55" s="28">
         <f>IF(F55="Pago",1,IF(G55=0,0.97,IF(G55&lt;=30,0.9,IF(G55&lt;=60,0.72,IF(G55&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -3394,8 +4013,8 @@
       <c r="A56" s="14" t="n"/>
       <c r="B56" s="14" t="n"/>
       <c r="C56" s="15" t="n"/>
-      <c r="D56" s="17" t="n"/>
-      <c r="E56" s="17" t="n"/>
+      <c r="D56" s="27" t="n"/>
+      <c r="E56" s="27" t="n"/>
       <c r="F56" s="14" t="n"/>
       <c r="G56" s="14">
         <f>IF(OR(F56="Pago",E56="",E56&gt;=TODAY()),0,TODAY()-E56)</f>
@@ -3405,7 +4024,7 @@
         <f>IF(F56="Pago","Pago",IF(G56=0,"A vencer",IF(G56&lt;=30,"1-30",IF(G56&lt;=60,"31-60",IF(G56&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I56" s="18">
+      <c r="I56" s="28">
         <f>IF(F56="Pago",1,IF(G56=0,0.97,IF(G56&lt;=30,0.9,IF(G56&lt;=60,0.72,IF(G56&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -3423,8 +4042,8 @@
       <c r="A57" s="14" t="n"/>
       <c r="B57" s="14" t="n"/>
       <c r="C57" s="15" t="n"/>
-      <c r="D57" s="17" t="n"/>
-      <c r="E57" s="17" t="n"/>
+      <c r="D57" s="27" t="n"/>
+      <c r="E57" s="27" t="n"/>
       <c r="F57" s="14" t="n"/>
       <c r="G57" s="14">
         <f>IF(OR(F57="Pago",E57="",E57&gt;=TODAY()),0,TODAY()-E57)</f>
@@ -3434,7 +4053,7 @@
         <f>IF(F57="Pago","Pago",IF(G57=0,"A vencer",IF(G57&lt;=30,"1-30",IF(G57&lt;=60,"31-60",IF(G57&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I57" s="18">
+      <c r="I57" s="28">
         <f>IF(F57="Pago",1,IF(G57=0,0.97,IF(G57&lt;=30,0.9,IF(G57&lt;=60,0.72,IF(G57&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -3452,8 +4071,8 @@
       <c r="A58" s="14" t="n"/>
       <c r="B58" s="14" t="n"/>
       <c r="C58" s="15" t="n"/>
-      <c r="D58" s="17" t="n"/>
-      <c r="E58" s="17" t="n"/>
+      <c r="D58" s="27" t="n"/>
+      <c r="E58" s="27" t="n"/>
       <c r="F58" s="14" t="n"/>
       <c r="G58" s="14">
         <f>IF(OR(F58="Pago",E58="",E58&gt;=TODAY()),0,TODAY()-E58)</f>
@@ -3463,7 +4082,7 @@
         <f>IF(F58="Pago","Pago",IF(G58=0,"A vencer",IF(G58&lt;=30,"1-30",IF(G58&lt;=60,"31-60",IF(G58&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I58" s="18">
+      <c r="I58" s="28">
         <f>IF(F58="Pago",1,IF(G58=0,0.97,IF(G58&lt;=30,0.9,IF(G58&lt;=60,0.72,IF(G58&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -3481,8 +4100,8 @@
       <c r="A59" s="14" t="n"/>
       <c r="B59" s="14" t="n"/>
       <c r="C59" s="15" t="n"/>
-      <c r="D59" s="17" t="n"/>
-      <c r="E59" s="17" t="n"/>
+      <c r="D59" s="27" t="n"/>
+      <c r="E59" s="27" t="n"/>
       <c r="F59" s="14" t="n"/>
       <c r="G59" s="14">
         <f>IF(OR(F59="Pago",E59="",E59&gt;=TODAY()),0,TODAY()-E59)</f>
@@ -3492,7 +4111,7 @@
         <f>IF(F59="Pago","Pago",IF(G59=0,"A vencer",IF(G59&lt;=30,"1-30",IF(G59&lt;=60,"31-60",IF(G59&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I59" s="18">
+      <c r="I59" s="28">
         <f>IF(F59="Pago",1,IF(G59=0,0.97,IF(G59&lt;=30,0.9,IF(G59&lt;=60,0.72,IF(G59&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -3510,8 +4129,8 @@
       <c r="A60" s="14" t="n"/>
       <c r="B60" s="14" t="n"/>
       <c r="C60" s="15" t="n"/>
-      <c r="D60" s="17" t="n"/>
-      <c r="E60" s="17" t="n"/>
+      <c r="D60" s="27" t="n"/>
+      <c r="E60" s="27" t="n"/>
       <c r="F60" s="14" t="n"/>
       <c r="G60" s="14">
         <f>IF(OR(F60="Pago",E60="",E60&gt;=TODAY()),0,TODAY()-E60)</f>
@@ -3521,7 +4140,7 @@
         <f>IF(F60="Pago","Pago",IF(G60=0,"A vencer",IF(G60&lt;=30,"1-30",IF(G60&lt;=60,"31-60",IF(G60&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I60" s="18">
+      <c r="I60" s="28">
         <f>IF(F60="Pago",1,IF(G60=0,0.97,IF(G60&lt;=30,0.9,IF(G60&lt;=60,0.72,IF(G60&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -3539,8 +4158,8 @@
       <c r="A61" s="14" t="n"/>
       <c r="B61" s="14" t="n"/>
       <c r="C61" s="15" t="n"/>
-      <c r="D61" s="17" t="n"/>
-      <c r="E61" s="17" t="n"/>
+      <c r="D61" s="27" t="n"/>
+      <c r="E61" s="27" t="n"/>
       <c r="F61" s="14" t="n"/>
       <c r="G61" s="14">
         <f>IF(OR(F61="Pago",E61="",E61&gt;=TODAY()),0,TODAY()-E61)</f>
@@ -3550,7 +4169,7 @@
         <f>IF(F61="Pago","Pago",IF(G61=0,"A vencer",IF(G61&lt;=30,"1-30",IF(G61&lt;=60,"31-60",IF(G61&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I61" s="18">
+      <c r="I61" s="28">
         <f>IF(F61="Pago",1,IF(G61=0,0.97,IF(G61&lt;=30,0.9,IF(G61&lt;=60,0.72,IF(G61&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -3568,8 +4187,8 @@
       <c r="A62" s="14" t="n"/>
       <c r="B62" s="14" t="n"/>
       <c r="C62" s="15" t="n"/>
-      <c r="D62" s="17" t="n"/>
-      <c r="E62" s="17" t="n"/>
+      <c r="D62" s="27" t="n"/>
+      <c r="E62" s="27" t="n"/>
       <c r="F62" s="14" t="n"/>
       <c r="G62" s="14">
         <f>IF(OR(F62="Pago",E62="",E62&gt;=TODAY()),0,TODAY()-E62)</f>
@@ -3579,7 +4198,7 @@
         <f>IF(F62="Pago","Pago",IF(G62=0,"A vencer",IF(G62&lt;=30,"1-30",IF(G62&lt;=60,"31-60",IF(G62&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I62" s="18">
+      <c r="I62" s="28">
         <f>IF(F62="Pago",1,IF(G62=0,0.97,IF(G62&lt;=30,0.9,IF(G62&lt;=60,0.72,IF(G62&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -3597,8 +4216,8 @@
       <c r="A63" s="14" t="n"/>
       <c r="B63" s="14" t="n"/>
       <c r="C63" s="15" t="n"/>
-      <c r="D63" s="17" t="n"/>
-      <c r="E63" s="17" t="n"/>
+      <c r="D63" s="27" t="n"/>
+      <c r="E63" s="27" t="n"/>
       <c r="F63" s="14" t="n"/>
       <c r="G63" s="14">
         <f>IF(OR(F63="Pago",E63="",E63&gt;=TODAY()),0,TODAY()-E63)</f>
@@ -3608,7 +4227,7 @@
         <f>IF(F63="Pago","Pago",IF(G63=0,"A vencer",IF(G63&lt;=30,"1-30",IF(G63&lt;=60,"31-60",IF(G63&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I63" s="18">
+      <c r="I63" s="28">
         <f>IF(F63="Pago",1,IF(G63=0,0.97,IF(G63&lt;=30,0.9,IF(G63&lt;=60,0.72,IF(G63&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -3626,8 +4245,8 @@
       <c r="A64" s="14" t="n"/>
       <c r="B64" s="14" t="n"/>
       <c r="C64" s="15" t="n"/>
-      <c r="D64" s="17" t="n"/>
-      <c r="E64" s="17" t="n"/>
+      <c r="D64" s="27" t="n"/>
+      <c r="E64" s="27" t="n"/>
       <c r="F64" s="14" t="n"/>
       <c r="G64" s="14">
         <f>IF(OR(F64="Pago",E64="",E64&gt;=TODAY()),0,TODAY()-E64)</f>
@@ -3637,7 +4256,7 @@
         <f>IF(F64="Pago","Pago",IF(G64=0,"A vencer",IF(G64&lt;=30,"1-30",IF(G64&lt;=60,"31-60",IF(G64&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I64" s="18">
+      <c r="I64" s="28">
         <f>IF(F64="Pago",1,IF(G64=0,0.97,IF(G64&lt;=30,0.9,IF(G64&lt;=60,0.72,IF(G64&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -3655,8 +4274,8 @@
       <c r="A65" s="14" t="n"/>
       <c r="B65" s="14" t="n"/>
       <c r="C65" s="15" t="n"/>
-      <c r="D65" s="17" t="n"/>
-      <c r="E65" s="17" t="n"/>
+      <c r="D65" s="27" t="n"/>
+      <c r="E65" s="27" t="n"/>
       <c r="F65" s="14" t="n"/>
       <c r="G65" s="14">
         <f>IF(OR(F65="Pago",E65="",E65&gt;=TODAY()),0,TODAY()-E65)</f>
@@ -3666,7 +4285,7 @@
         <f>IF(F65="Pago","Pago",IF(G65=0,"A vencer",IF(G65&lt;=30,"1-30",IF(G65&lt;=60,"31-60",IF(G65&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I65" s="18">
+      <c r="I65" s="28">
         <f>IF(F65="Pago",1,IF(G65=0,0.97,IF(G65&lt;=30,0.9,IF(G65&lt;=60,0.72,IF(G65&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -3684,8 +4303,8 @@
       <c r="A66" s="14" t="n"/>
       <c r="B66" s="14" t="n"/>
       <c r="C66" s="15" t="n"/>
-      <c r="D66" s="17" t="n"/>
-      <c r="E66" s="17" t="n"/>
+      <c r="D66" s="27" t="n"/>
+      <c r="E66" s="27" t="n"/>
       <c r="F66" s="14" t="n"/>
       <c r="G66" s="14">
         <f>IF(OR(F66="Pago",E66="",E66&gt;=TODAY()),0,TODAY()-E66)</f>
@@ -3695,7 +4314,7 @@
         <f>IF(F66="Pago","Pago",IF(G66=0,"A vencer",IF(G66&lt;=30,"1-30",IF(G66&lt;=60,"31-60",IF(G66&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I66" s="18">
+      <c r="I66" s="28">
         <f>IF(F66="Pago",1,IF(G66=0,0.97,IF(G66&lt;=30,0.9,IF(G66&lt;=60,0.72,IF(G66&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -3713,8 +4332,8 @@
       <c r="A67" s="14" t="n"/>
       <c r="B67" s="14" t="n"/>
       <c r="C67" s="15" t="n"/>
-      <c r="D67" s="17" t="n"/>
-      <c r="E67" s="17" t="n"/>
+      <c r="D67" s="27" t="n"/>
+      <c r="E67" s="27" t="n"/>
       <c r="F67" s="14" t="n"/>
       <c r="G67" s="14">
         <f>IF(OR(F67="Pago",E67="",E67&gt;=TODAY()),0,TODAY()-E67)</f>
@@ -3724,7 +4343,7 @@
         <f>IF(F67="Pago","Pago",IF(G67=0,"A vencer",IF(G67&lt;=30,"1-30",IF(G67&lt;=60,"31-60",IF(G67&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I67" s="18">
+      <c r="I67" s="28">
         <f>IF(F67="Pago",1,IF(G67=0,0.97,IF(G67&lt;=30,0.9,IF(G67&lt;=60,0.72,IF(G67&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -3742,8 +4361,8 @@
       <c r="A68" s="14" t="n"/>
       <c r="B68" s="14" t="n"/>
       <c r="C68" s="15" t="n"/>
-      <c r="D68" s="17" t="n"/>
-      <c r="E68" s="17" t="n"/>
+      <c r="D68" s="27" t="n"/>
+      <c r="E68" s="27" t="n"/>
       <c r="F68" s="14" t="n"/>
       <c r="G68" s="14">
         <f>IF(OR(F68="Pago",E68="",E68&gt;=TODAY()),0,TODAY()-E68)</f>
@@ -3753,7 +4372,7 @@
         <f>IF(F68="Pago","Pago",IF(G68=0,"A vencer",IF(G68&lt;=30,"1-30",IF(G68&lt;=60,"31-60",IF(G68&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I68" s="18">
+      <c r="I68" s="28">
         <f>IF(F68="Pago",1,IF(G68=0,0.97,IF(G68&lt;=30,0.9,IF(G68&lt;=60,0.72,IF(G68&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -3771,8 +4390,8 @@
       <c r="A69" s="14" t="n"/>
       <c r="B69" s="14" t="n"/>
       <c r="C69" s="15" t="n"/>
-      <c r="D69" s="17" t="n"/>
-      <c r="E69" s="17" t="n"/>
+      <c r="D69" s="27" t="n"/>
+      <c r="E69" s="27" t="n"/>
       <c r="F69" s="14" t="n"/>
       <c r="G69" s="14">
         <f>IF(OR(F69="Pago",E69="",E69&gt;=TODAY()),0,TODAY()-E69)</f>
@@ -3782,7 +4401,7 @@
         <f>IF(F69="Pago","Pago",IF(G69=0,"A vencer",IF(G69&lt;=30,"1-30",IF(G69&lt;=60,"31-60",IF(G69&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I69" s="18">
+      <c r="I69" s="28">
         <f>IF(F69="Pago",1,IF(G69=0,0.97,IF(G69&lt;=30,0.9,IF(G69&lt;=60,0.72,IF(G69&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -3800,8 +4419,8 @@
       <c r="A70" s="14" t="n"/>
       <c r="B70" s="14" t="n"/>
       <c r="C70" s="15" t="n"/>
-      <c r="D70" s="17" t="n"/>
-      <c r="E70" s="17" t="n"/>
+      <c r="D70" s="27" t="n"/>
+      <c r="E70" s="27" t="n"/>
       <c r="F70" s="14" t="n"/>
       <c r="G70" s="14">
         <f>IF(OR(F70="Pago",E70="",E70&gt;=TODAY()),0,TODAY()-E70)</f>
@@ -3811,7 +4430,7 @@
         <f>IF(F70="Pago","Pago",IF(G70=0,"A vencer",IF(G70&lt;=30,"1-30",IF(G70&lt;=60,"31-60",IF(G70&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I70" s="18">
+      <c r="I70" s="28">
         <f>IF(F70="Pago",1,IF(G70=0,0.97,IF(G70&lt;=30,0.9,IF(G70&lt;=60,0.72,IF(G70&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -3829,8 +4448,8 @@
       <c r="A71" s="14" t="n"/>
       <c r="B71" s="14" t="n"/>
       <c r="C71" s="15" t="n"/>
-      <c r="D71" s="17" t="n"/>
-      <c r="E71" s="17" t="n"/>
+      <c r="D71" s="27" t="n"/>
+      <c r="E71" s="27" t="n"/>
       <c r="F71" s="14" t="n"/>
       <c r="G71" s="14">
         <f>IF(OR(F71="Pago",E71="",E71&gt;=TODAY()),0,TODAY()-E71)</f>
@@ -3840,7 +4459,7 @@
         <f>IF(F71="Pago","Pago",IF(G71=0,"A vencer",IF(G71&lt;=30,"1-30",IF(G71&lt;=60,"31-60",IF(G71&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I71" s="18">
+      <c r="I71" s="28">
         <f>IF(F71="Pago",1,IF(G71=0,0.97,IF(G71&lt;=30,0.9,IF(G71&lt;=60,0.72,IF(G71&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -3858,8 +4477,8 @@
       <c r="A72" s="14" t="n"/>
       <c r="B72" s="14" t="n"/>
       <c r="C72" s="15" t="n"/>
-      <c r="D72" s="17" t="n"/>
-      <c r="E72" s="17" t="n"/>
+      <c r="D72" s="27" t="n"/>
+      <c r="E72" s="27" t="n"/>
       <c r="F72" s="14" t="n"/>
       <c r="G72" s="14">
         <f>IF(OR(F72="Pago",E72="",E72&gt;=TODAY()),0,TODAY()-E72)</f>
@@ -3869,7 +4488,7 @@
         <f>IF(F72="Pago","Pago",IF(G72=0,"A vencer",IF(G72&lt;=30,"1-30",IF(G72&lt;=60,"31-60",IF(G72&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I72" s="18">
+      <c r="I72" s="28">
         <f>IF(F72="Pago",1,IF(G72=0,0.97,IF(G72&lt;=30,0.9,IF(G72&lt;=60,0.72,IF(G72&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -3887,8 +4506,8 @@
       <c r="A73" s="14" t="n"/>
       <c r="B73" s="14" t="n"/>
       <c r="C73" s="15" t="n"/>
-      <c r="D73" s="17" t="n"/>
-      <c r="E73" s="17" t="n"/>
+      <c r="D73" s="27" t="n"/>
+      <c r="E73" s="27" t="n"/>
       <c r="F73" s="14" t="n"/>
       <c r="G73" s="14">
         <f>IF(OR(F73="Pago",E73="",E73&gt;=TODAY()),0,TODAY()-E73)</f>
@@ -3898,7 +4517,7 @@
         <f>IF(F73="Pago","Pago",IF(G73=0,"A vencer",IF(G73&lt;=30,"1-30",IF(G73&lt;=60,"31-60",IF(G73&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I73" s="18">
+      <c r="I73" s="28">
         <f>IF(F73="Pago",1,IF(G73=0,0.97,IF(G73&lt;=30,0.9,IF(G73&lt;=60,0.72,IF(G73&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -3916,8 +4535,8 @@
       <c r="A74" s="14" t="n"/>
       <c r="B74" s="14" t="n"/>
       <c r="C74" s="15" t="n"/>
-      <c r="D74" s="17" t="n"/>
-      <c r="E74" s="17" t="n"/>
+      <c r="D74" s="27" t="n"/>
+      <c r="E74" s="27" t="n"/>
       <c r="F74" s="14" t="n"/>
       <c r="G74" s="14">
         <f>IF(OR(F74="Pago",E74="",E74&gt;=TODAY()),0,TODAY()-E74)</f>
@@ -3927,7 +4546,7 @@
         <f>IF(F74="Pago","Pago",IF(G74=0,"A vencer",IF(G74&lt;=30,"1-30",IF(G74&lt;=60,"31-60",IF(G74&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I74" s="18">
+      <c r="I74" s="28">
         <f>IF(F74="Pago",1,IF(G74=0,0.97,IF(G74&lt;=30,0.9,IF(G74&lt;=60,0.72,IF(G74&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -3945,8 +4564,8 @@
       <c r="A75" s="14" t="n"/>
       <c r="B75" s="14" t="n"/>
       <c r="C75" s="15" t="n"/>
-      <c r="D75" s="17" t="n"/>
-      <c r="E75" s="17" t="n"/>
+      <c r="D75" s="27" t="n"/>
+      <c r="E75" s="27" t="n"/>
       <c r="F75" s="14" t="n"/>
       <c r="G75" s="14">
         <f>IF(OR(F75="Pago",E75="",E75&gt;=TODAY()),0,TODAY()-E75)</f>
@@ -3956,7 +4575,7 @@
         <f>IF(F75="Pago","Pago",IF(G75=0,"A vencer",IF(G75&lt;=30,"1-30",IF(G75&lt;=60,"31-60",IF(G75&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I75" s="18">
+      <c r="I75" s="28">
         <f>IF(F75="Pago",1,IF(G75=0,0.97,IF(G75&lt;=30,0.9,IF(G75&lt;=60,0.72,IF(G75&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -3974,8 +4593,8 @@
       <c r="A76" s="14" t="n"/>
       <c r="B76" s="14" t="n"/>
       <c r="C76" s="15" t="n"/>
-      <c r="D76" s="17" t="n"/>
-      <c r="E76" s="17" t="n"/>
+      <c r="D76" s="27" t="n"/>
+      <c r="E76" s="27" t="n"/>
       <c r="F76" s="14" t="n"/>
       <c r="G76" s="14">
         <f>IF(OR(F76="Pago",E76="",E76&gt;=TODAY()),0,TODAY()-E76)</f>
@@ -3985,7 +4604,7 @@
         <f>IF(F76="Pago","Pago",IF(G76=0,"A vencer",IF(G76&lt;=30,"1-30",IF(G76&lt;=60,"31-60",IF(G76&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I76" s="18">
+      <c r="I76" s="28">
         <f>IF(F76="Pago",1,IF(G76=0,0.97,IF(G76&lt;=30,0.9,IF(G76&lt;=60,0.72,IF(G76&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -4003,8 +4622,8 @@
       <c r="A77" s="14" t="n"/>
       <c r="B77" s="14" t="n"/>
       <c r="C77" s="15" t="n"/>
-      <c r="D77" s="17" t="n"/>
-      <c r="E77" s="17" t="n"/>
+      <c r="D77" s="27" t="n"/>
+      <c r="E77" s="27" t="n"/>
       <c r="F77" s="14" t="n"/>
       <c r="G77" s="14">
         <f>IF(OR(F77="Pago",E77="",E77&gt;=TODAY()),0,TODAY()-E77)</f>
@@ -4014,7 +4633,7 @@
         <f>IF(F77="Pago","Pago",IF(G77=0,"A vencer",IF(G77&lt;=30,"1-30",IF(G77&lt;=60,"31-60",IF(G77&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I77" s="18">
+      <c r="I77" s="28">
         <f>IF(F77="Pago",1,IF(G77=0,0.97,IF(G77&lt;=30,0.9,IF(G77&lt;=60,0.72,IF(G77&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -4032,8 +4651,8 @@
       <c r="A78" s="14" t="n"/>
       <c r="B78" s="14" t="n"/>
       <c r="C78" s="15" t="n"/>
-      <c r="D78" s="17" t="n"/>
-      <c r="E78" s="17" t="n"/>
+      <c r="D78" s="27" t="n"/>
+      <c r="E78" s="27" t="n"/>
       <c r="F78" s="14" t="n"/>
       <c r="G78" s="14">
         <f>IF(OR(F78="Pago",E78="",E78&gt;=TODAY()),0,TODAY()-E78)</f>
@@ -4043,7 +4662,7 @@
         <f>IF(F78="Pago","Pago",IF(G78=0,"A vencer",IF(G78&lt;=30,"1-30",IF(G78&lt;=60,"31-60",IF(G78&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I78" s="18">
+      <c r="I78" s="28">
         <f>IF(F78="Pago",1,IF(G78=0,0.97,IF(G78&lt;=30,0.9,IF(G78&lt;=60,0.72,IF(G78&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -4061,8 +4680,8 @@
       <c r="A79" s="14" t="n"/>
       <c r="B79" s="14" t="n"/>
       <c r="C79" s="15" t="n"/>
-      <c r="D79" s="17" t="n"/>
-      <c r="E79" s="17" t="n"/>
+      <c r="D79" s="27" t="n"/>
+      <c r="E79" s="27" t="n"/>
       <c r="F79" s="14" t="n"/>
       <c r="G79" s="14">
         <f>IF(OR(F79="Pago",E79="",E79&gt;=TODAY()),0,TODAY()-E79)</f>
@@ -4072,7 +4691,7 @@
         <f>IF(F79="Pago","Pago",IF(G79=0,"A vencer",IF(G79&lt;=30,"1-30",IF(G79&lt;=60,"31-60",IF(G79&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I79" s="18">
+      <c r="I79" s="28">
         <f>IF(F79="Pago",1,IF(G79=0,0.97,IF(G79&lt;=30,0.9,IF(G79&lt;=60,0.72,IF(G79&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -4090,8 +4709,8 @@
       <c r="A80" s="14" t="n"/>
       <c r="B80" s="14" t="n"/>
       <c r="C80" s="15" t="n"/>
-      <c r="D80" s="17" t="n"/>
-      <c r="E80" s="17" t="n"/>
+      <c r="D80" s="27" t="n"/>
+      <c r="E80" s="27" t="n"/>
       <c r="F80" s="14" t="n"/>
       <c r="G80" s="14">
         <f>IF(OR(F80="Pago",E80="",E80&gt;=TODAY()),0,TODAY()-E80)</f>
@@ -4101,7 +4720,7 @@
         <f>IF(F80="Pago","Pago",IF(G80=0,"A vencer",IF(G80&lt;=30,"1-30",IF(G80&lt;=60,"31-60",IF(G80&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I80" s="18">
+      <c r="I80" s="28">
         <f>IF(F80="Pago",1,IF(G80=0,0.97,IF(G80&lt;=30,0.9,IF(G80&lt;=60,0.72,IF(G80&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -4119,8 +4738,8 @@
       <c r="A81" s="14" t="n"/>
       <c r="B81" s="14" t="n"/>
       <c r="C81" s="15" t="n"/>
-      <c r="D81" s="17" t="n"/>
-      <c r="E81" s="17" t="n"/>
+      <c r="D81" s="27" t="n"/>
+      <c r="E81" s="27" t="n"/>
       <c r="F81" s="14" t="n"/>
       <c r="G81" s="14">
         <f>IF(OR(F81="Pago",E81="",E81&gt;=TODAY()),0,TODAY()-E81)</f>
@@ -4130,7 +4749,7 @@
         <f>IF(F81="Pago","Pago",IF(G81=0,"A vencer",IF(G81&lt;=30,"1-30",IF(G81&lt;=60,"31-60",IF(G81&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I81" s="18">
+      <c r="I81" s="28">
         <f>IF(F81="Pago",1,IF(G81=0,0.97,IF(G81&lt;=30,0.9,IF(G81&lt;=60,0.72,IF(G81&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -4148,8 +4767,8 @@
       <c r="A82" s="14" t="n"/>
       <c r="B82" s="14" t="n"/>
       <c r="C82" s="15" t="n"/>
-      <c r="D82" s="17" t="n"/>
-      <c r="E82" s="17" t="n"/>
+      <c r="D82" s="27" t="n"/>
+      <c r="E82" s="27" t="n"/>
       <c r="F82" s="14" t="n"/>
       <c r="G82" s="14">
         <f>IF(OR(F82="Pago",E82="",E82&gt;=TODAY()),0,TODAY()-E82)</f>
@@ -4159,7 +4778,7 @@
         <f>IF(F82="Pago","Pago",IF(G82=0,"A vencer",IF(G82&lt;=30,"1-30",IF(G82&lt;=60,"31-60",IF(G82&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I82" s="18">
+      <c r="I82" s="28">
         <f>IF(F82="Pago",1,IF(G82=0,0.97,IF(G82&lt;=30,0.9,IF(G82&lt;=60,0.72,IF(G82&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -4177,8 +4796,8 @@
       <c r="A83" s="14" t="n"/>
       <c r="B83" s="14" t="n"/>
       <c r="C83" s="15" t="n"/>
-      <c r="D83" s="17" t="n"/>
-      <c r="E83" s="17" t="n"/>
+      <c r="D83" s="27" t="n"/>
+      <c r="E83" s="27" t="n"/>
       <c r="F83" s="14" t="n"/>
       <c r="G83" s="14">
         <f>IF(OR(F83="Pago",E83="",E83&gt;=TODAY()),0,TODAY()-E83)</f>
@@ -4188,7 +4807,7 @@
         <f>IF(F83="Pago","Pago",IF(G83=0,"A vencer",IF(G83&lt;=30,"1-30",IF(G83&lt;=60,"31-60",IF(G83&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I83" s="18">
+      <c r="I83" s="28">
         <f>IF(F83="Pago",1,IF(G83=0,0.97,IF(G83&lt;=30,0.9,IF(G83&lt;=60,0.72,IF(G83&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -4206,8 +4825,8 @@
       <c r="A84" s="14" t="n"/>
       <c r="B84" s="14" t="n"/>
       <c r="C84" s="15" t="n"/>
-      <c r="D84" s="17" t="n"/>
-      <c r="E84" s="17" t="n"/>
+      <c r="D84" s="27" t="n"/>
+      <c r="E84" s="27" t="n"/>
       <c r="F84" s="14" t="n"/>
       <c r="G84" s="14">
         <f>IF(OR(F84="Pago",E84="",E84&gt;=TODAY()),0,TODAY()-E84)</f>
@@ -4217,7 +4836,7 @@
         <f>IF(F84="Pago","Pago",IF(G84=0,"A vencer",IF(G84&lt;=30,"1-30",IF(G84&lt;=60,"31-60",IF(G84&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I84" s="18">
+      <c r="I84" s="28">
         <f>IF(F84="Pago",1,IF(G84=0,0.97,IF(G84&lt;=30,0.9,IF(G84&lt;=60,0.72,IF(G84&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -4235,8 +4854,8 @@
       <c r="A85" s="14" t="n"/>
       <c r="B85" s="14" t="n"/>
       <c r="C85" s="15" t="n"/>
-      <c r="D85" s="17" t="n"/>
-      <c r="E85" s="17" t="n"/>
+      <c r="D85" s="27" t="n"/>
+      <c r="E85" s="27" t="n"/>
       <c r="F85" s="14" t="n"/>
       <c r="G85" s="14">
         <f>IF(OR(F85="Pago",E85="",E85&gt;=TODAY()),0,TODAY()-E85)</f>
@@ -4246,7 +4865,7 @@
         <f>IF(F85="Pago","Pago",IF(G85=0,"A vencer",IF(G85&lt;=30,"1-30",IF(G85&lt;=60,"31-60",IF(G85&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I85" s="18">
+      <c r="I85" s="28">
         <f>IF(F85="Pago",1,IF(G85=0,0.97,IF(G85&lt;=30,0.9,IF(G85&lt;=60,0.72,IF(G85&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -4264,8 +4883,8 @@
       <c r="A86" s="14" t="n"/>
       <c r="B86" s="14" t="n"/>
       <c r="C86" s="15" t="n"/>
-      <c r="D86" s="17" t="n"/>
-      <c r="E86" s="17" t="n"/>
+      <c r="D86" s="27" t="n"/>
+      <c r="E86" s="27" t="n"/>
       <c r="F86" s="14" t="n"/>
       <c r="G86" s="14">
         <f>IF(OR(F86="Pago",E86="",E86&gt;=TODAY()),0,TODAY()-E86)</f>
@@ -4275,7 +4894,7 @@
         <f>IF(F86="Pago","Pago",IF(G86=0,"A vencer",IF(G86&lt;=30,"1-30",IF(G86&lt;=60,"31-60",IF(G86&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I86" s="18">
+      <c r="I86" s="28">
         <f>IF(F86="Pago",1,IF(G86=0,0.97,IF(G86&lt;=30,0.9,IF(G86&lt;=60,0.72,IF(G86&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -4293,8 +4912,8 @@
       <c r="A87" s="14" t="n"/>
       <c r="B87" s="14" t="n"/>
       <c r="C87" s="15" t="n"/>
-      <c r="D87" s="17" t="n"/>
-      <c r="E87" s="17" t="n"/>
+      <c r="D87" s="27" t="n"/>
+      <c r="E87" s="27" t="n"/>
       <c r="F87" s="14" t="n"/>
       <c r="G87" s="14">
         <f>IF(OR(F87="Pago",E87="",E87&gt;=TODAY()),0,TODAY()-E87)</f>
@@ -4304,7 +4923,7 @@
         <f>IF(F87="Pago","Pago",IF(G87=0,"A vencer",IF(G87&lt;=30,"1-30",IF(G87&lt;=60,"31-60",IF(G87&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I87" s="18">
+      <c r="I87" s="28">
         <f>IF(F87="Pago",1,IF(G87=0,0.97,IF(G87&lt;=30,0.9,IF(G87&lt;=60,0.72,IF(G87&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -4322,8 +4941,8 @@
       <c r="A88" s="14" t="n"/>
       <c r="B88" s="14" t="n"/>
       <c r="C88" s="15" t="n"/>
-      <c r="D88" s="17" t="n"/>
-      <c r="E88" s="17" t="n"/>
+      <c r="D88" s="27" t="n"/>
+      <c r="E88" s="27" t="n"/>
       <c r="F88" s="14" t="n"/>
       <c r="G88" s="14">
         <f>IF(OR(F88="Pago",E88="",E88&gt;=TODAY()),0,TODAY()-E88)</f>
@@ -4333,7 +4952,7 @@
         <f>IF(F88="Pago","Pago",IF(G88=0,"A vencer",IF(G88&lt;=30,"1-30",IF(G88&lt;=60,"31-60",IF(G88&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I88" s="18">
+      <c r="I88" s="28">
         <f>IF(F88="Pago",1,IF(G88=0,0.97,IF(G88&lt;=30,0.9,IF(G88&lt;=60,0.72,IF(G88&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -4351,8 +4970,8 @@
       <c r="A89" s="14" t="n"/>
       <c r="B89" s="14" t="n"/>
       <c r="C89" s="15" t="n"/>
-      <c r="D89" s="17" t="n"/>
-      <c r="E89" s="17" t="n"/>
+      <c r="D89" s="27" t="n"/>
+      <c r="E89" s="27" t="n"/>
       <c r="F89" s="14" t="n"/>
       <c r="G89" s="14">
         <f>IF(OR(F89="Pago",E89="",E89&gt;=TODAY()),0,TODAY()-E89)</f>
@@ -4362,7 +4981,7 @@
         <f>IF(F89="Pago","Pago",IF(G89=0,"A vencer",IF(G89&lt;=30,"1-30",IF(G89&lt;=60,"31-60",IF(G89&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I89" s="18">
+      <c r="I89" s="28">
         <f>IF(F89="Pago",1,IF(G89=0,0.97,IF(G89&lt;=30,0.9,IF(G89&lt;=60,0.72,IF(G89&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -4380,8 +4999,8 @@
       <c r="A90" s="14" t="n"/>
       <c r="B90" s="14" t="n"/>
       <c r="C90" s="15" t="n"/>
-      <c r="D90" s="17" t="n"/>
-      <c r="E90" s="17" t="n"/>
+      <c r="D90" s="27" t="n"/>
+      <c r="E90" s="27" t="n"/>
       <c r="F90" s="14" t="n"/>
       <c r="G90" s="14">
         <f>IF(OR(F90="Pago",E90="",E90&gt;=TODAY()),0,TODAY()-E90)</f>
@@ -4391,7 +5010,7 @@
         <f>IF(F90="Pago","Pago",IF(G90=0,"A vencer",IF(G90&lt;=30,"1-30",IF(G90&lt;=60,"31-60",IF(G90&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I90" s="18">
+      <c r="I90" s="28">
         <f>IF(F90="Pago",1,IF(G90=0,0.97,IF(G90&lt;=30,0.9,IF(G90&lt;=60,0.72,IF(G90&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -4409,8 +5028,8 @@
       <c r="A91" s="14" t="n"/>
       <c r="B91" s="14" t="n"/>
       <c r="C91" s="15" t="n"/>
-      <c r="D91" s="17" t="n"/>
-      <c r="E91" s="17" t="n"/>
+      <c r="D91" s="27" t="n"/>
+      <c r="E91" s="27" t="n"/>
       <c r="F91" s="14" t="n"/>
       <c r="G91" s="14">
         <f>IF(OR(F91="Pago",E91="",E91&gt;=TODAY()),0,TODAY()-E91)</f>
@@ -4420,7 +5039,7 @@
         <f>IF(F91="Pago","Pago",IF(G91=0,"A vencer",IF(G91&lt;=30,"1-30",IF(G91&lt;=60,"31-60",IF(G91&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I91" s="18">
+      <c r="I91" s="28">
         <f>IF(F91="Pago",1,IF(G91=0,0.97,IF(G91&lt;=30,0.9,IF(G91&lt;=60,0.72,IF(G91&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -4438,8 +5057,8 @@
       <c r="A92" s="14" t="n"/>
       <c r="B92" s="14" t="n"/>
       <c r="C92" s="15" t="n"/>
-      <c r="D92" s="17" t="n"/>
-      <c r="E92" s="17" t="n"/>
+      <c r="D92" s="27" t="n"/>
+      <c r="E92" s="27" t="n"/>
       <c r="F92" s="14" t="n"/>
       <c r="G92" s="14">
         <f>IF(OR(F92="Pago",E92="",E92&gt;=TODAY()),0,TODAY()-E92)</f>
@@ -4449,7 +5068,7 @@
         <f>IF(F92="Pago","Pago",IF(G92=0,"A vencer",IF(G92&lt;=30,"1-30",IF(G92&lt;=60,"31-60",IF(G92&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I92" s="18">
+      <c r="I92" s="28">
         <f>IF(F92="Pago",1,IF(G92=0,0.97,IF(G92&lt;=30,0.9,IF(G92&lt;=60,0.72,IF(G92&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -4467,8 +5086,8 @@
       <c r="A93" s="14" t="n"/>
       <c r="B93" s="14" t="n"/>
       <c r="C93" s="15" t="n"/>
-      <c r="D93" s="17" t="n"/>
-      <c r="E93" s="17" t="n"/>
+      <c r="D93" s="27" t="n"/>
+      <c r="E93" s="27" t="n"/>
       <c r="F93" s="14" t="n"/>
       <c r="G93" s="14">
         <f>IF(OR(F93="Pago",E93="",E93&gt;=TODAY()),0,TODAY()-E93)</f>
@@ -4478,7 +5097,7 @@
         <f>IF(F93="Pago","Pago",IF(G93=0,"A vencer",IF(G93&lt;=30,"1-30",IF(G93&lt;=60,"31-60",IF(G93&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I93" s="18">
+      <c r="I93" s="28">
         <f>IF(F93="Pago",1,IF(G93=0,0.97,IF(G93&lt;=30,0.9,IF(G93&lt;=60,0.72,IF(G93&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -4496,8 +5115,8 @@
       <c r="A94" s="14" t="n"/>
       <c r="B94" s="14" t="n"/>
       <c r="C94" s="15" t="n"/>
-      <c r="D94" s="17" t="n"/>
-      <c r="E94" s="17" t="n"/>
+      <c r="D94" s="27" t="n"/>
+      <c r="E94" s="27" t="n"/>
       <c r="F94" s="14" t="n"/>
       <c r="G94" s="14">
         <f>IF(OR(F94="Pago",E94="",E94&gt;=TODAY()),0,TODAY()-E94)</f>
@@ -4507,7 +5126,7 @@
         <f>IF(F94="Pago","Pago",IF(G94=0,"A vencer",IF(G94&lt;=30,"1-30",IF(G94&lt;=60,"31-60",IF(G94&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I94" s="18">
+      <c r="I94" s="28">
         <f>IF(F94="Pago",1,IF(G94=0,0.97,IF(G94&lt;=30,0.9,IF(G94&lt;=60,0.72,IF(G94&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -4525,8 +5144,8 @@
       <c r="A95" s="14" t="n"/>
       <c r="B95" s="14" t="n"/>
       <c r="C95" s="15" t="n"/>
-      <c r="D95" s="17" t="n"/>
-      <c r="E95" s="17" t="n"/>
+      <c r="D95" s="27" t="n"/>
+      <c r="E95" s="27" t="n"/>
       <c r="F95" s="14" t="n"/>
       <c r="G95" s="14">
         <f>IF(OR(F95="Pago",E95="",E95&gt;=TODAY()),0,TODAY()-E95)</f>
@@ -4536,7 +5155,7 @@
         <f>IF(F95="Pago","Pago",IF(G95=0,"A vencer",IF(G95&lt;=30,"1-30",IF(G95&lt;=60,"31-60",IF(G95&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I95" s="18">
+      <c r="I95" s="28">
         <f>IF(F95="Pago",1,IF(G95=0,0.97,IF(G95&lt;=30,0.9,IF(G95&lt;=60,0.72,IF(G95&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -4554,8 +5173,8 @@
       <c r="A96" s="14" t="n"/>
       <c r="B96" s="14" t="n"/>
       <c r="C96" s="15" t="n"/>
-      <c r="D96" s="17" t="n"/>
-      <c r="E96" s="17" t="n"/>
+      <c r="D96" s="27" t="n"/>
+      <c r="E96" s="27" t="n"/>
       <c r="F96" s="14" t="n"/>
       <c r="G96" s="14">
         <f>IF(OR(F96="Pago",E96="",E96&gt;=TODAY()),0,TODAY()-E96)</f>
@@ -4565,7 +5184,7 @@
         <f>IF(F96="Pago","Pago",IF(G96=0,"A vencer",IF(G96&lt;=30,"1-30",IF(G96&lt;=60,"31-60",IF(G96&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I96" s="18">
+      <c r="I96" s="28">
         <f>IF(F96="Pago",1,IF(G96=0,0.97,IF(G96&lt;=30,0.9,IF(G96&lt;=60,0.72,IF(G96&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -4583,8 +5202,8 @@
       <c r="A97" s="14" t="n"/>
       <c r="B97" s="14" t="n"/>
       <c r="C97" s="15" t="n"/>
-      <c r="D97" s="17" t="n"/>
-      <c r="E97" s="17" t="n"/>
+      <c r="D97" s="27" t="n"/>
+      <c r="E97" s="27" t="n"/>
       <c r="F97" s="14" t="n"/>
       <c r="G97" s="14">
         <f>IF(OR(F97="Pago",E97="",E97&gt;=TODAY()),0,TODAY()-E97)</f>
@@ -4594,7 +5213,7 @@
         <f>IF(F97="Pago","Pago",IF(G97=0,"A vencer",IF(G97&lt;=30,"1-30",IF(G97&lt;=60,"31-60",IF(G97&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I97" s="18">
+      <c r="I97" s="28">
         <f>IF(F97="Pago",1,IF(G97=0,0.97,IF(G97&lt;=30,0.9,IF(G97&lt;=60,0.72,IF(G97&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -4612,8 +5231,8 @@
       <c r="A98" s="14" t="n"/>
       <c r="B98" s="14" t="n"/>
       <c r="C98" s="15" t="n"/>
-      <c r="D98" s="17" t="n"/>
-      <c r="E98" s="17" t="n"/>
+      <c r="D98" s="27" t="n"/>
+      <c r="E98" s="27" t="n"/>
       <c r="F98" s="14" t="n"/>
       <c r="G98" s="14">
         <f>IF(OR(F98="Pago",E98="",E98&gt;=TODAY()),0,TODAY()-E98)</f>
@@ -4623,7 +5242,7 @@
         <f>IF(F98="Pago","Pago",IF(G98=0,"A vencer",IF(G98&lt;=30,"1-30",IF(G98&lt;=60,"31-60",IF(G98&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I98" s="18">
+      <c r="I98" s="28">
         <f>IF(F98="Pago",1,IF(G98=0,0.97,IF(G98&lt;=30,0.9,IF(G98&lt;=60,0.72,IF(G98&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -4641,8 +5260,8 @@
       <c r="A99" s="14" t="n"/>
       <c r="B99" s="14" t="n"/>
       <c r="C99" s="15" t="n"/>
-      <c r="D99" s="17" t="n"/>
-      <c r="E99" s="17" t="n"/>
+      <c r="D99" s="27" t="n"/>
+      <c r="E99" s="27" t="n"/>
       <c r="F99" s="14" t="n"/>
       <c r="G99" s="14">
         <f>IF(OR(F99="Pago",E99="",E99&gt;=TODAY()),0,TODAY()-E99)</f>
@@ -4652,7 +5271,7 @@
         <f>IF(F99="Pago","Pago",IF(G99=0,"A vencer",IF(G99&lt;=30,"1-30",IF(G99&lt;=60,"31-60",IF(G99&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I99" s="18">
+      <c r="I99" s="28">
         <f>IF(F99="Pago",1,IF(G99=0,0.97,IF(G99&lt;=30,0.9,IF(G99&lt;=60,0.72,IF(G99&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -4670,8 +5289,8 @@
       <c r="A100" s="14" t="n"/>
       <c r="B100" s="14" t="n"/>
       <c r="C100" s="15" t="n"/>
-      <c r="D100" s="17" t="n"/>
-      <c r="E100" s="17" t="n"/>
+      <c r="D100" s="27" t="n"/>
+      <c r="E100" s="27" t="n"/>
       <c r="F100" s="14" t="n"/>
       <c r="G100" s="14">
         <f>IF(OR(F100="Pago",E100="",E100&gt;=TODAY()),0,TODAY()-E100)</f>
@@ -4681,7 +5300,7 @@
         <f>IF(F100="Pago","Pago",IF(G100=0,"A vencer",IF(G100&lt;=30,"1-30",IF(G100&lt;=60,"31-60",IF(G100&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I100" s="18">
+      <c r="I100" s="28">
         <f>IF(F100="Pago",1,IF(G100=0,0.97,IF(G100&lt;=30,0.9,IF(G100&lt;=60,0.72,IF(G100&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -4699,8 +5318,8 @@
       <c r="A101" s="14" t="n"/>
       <c r="B101" s="14" t="n"/>
       <c r="C101" s="15" t="n"/>
-      <c r="D101" s="17" t="n"/>
-      <c r="E101" s="17" t="n"/>
+      <c r="D101" s="27" t="n"/>
+      <c r="E101" s="27" t="n"/>
       <c r="F101" s="14" t="n"/>
       <c r="G101" s="14">
         <f>IF(OR(F101="Pago",E101="",E101&gt;=TODAY()),0,TODAY()-E101)</f>
@@ -4710,7 +5329,7 @@
         <f>IF(F101="Pago","Pago",IF(G101=0,"A vencer",IF(G101&lt;=30,"1-30",IF(G101&lt;=60,"31-60",IF(G101&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I101" s="18">
+      <c r="I101" s="28">
         <f>IF(F101="Pago",1,IF(G101=0,0.97,IF(G101&lt;=30,0.9,IF(G101&lt;=60,0.72,IF(G101&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -4728,8 +5347,8 @@
       <c r="A102" s="14" t="n"/>
       <c r="B102" s="14" t="n"/>
       <c r="C102" s="15" t="n"/>
-      <c r="D102" s="17" t="n"/>
-      <c r="E102" s="17" t="n"/>
+      <c r="D102" s="27" t="n"/>
+      <c r="E102" s="27" t="n"/>
       <c r="F102" s="14" t="n"/>
       <c r="G102" s="14">
         <f>IF(OR(F102="Pago",E102="",E102&gt;=TODAY()),0,TODAY()-E102)</f>
@@ -4739,7 +5358,7 @@
         <f>IF(F102="Pago","Pago",IF(G102=0,"A vencer",IF(G102&lt;=30,"1-30",IF(G102&lt;=60,"31-60",IF(G102&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I102" s="18">
+      <c r="I102" s="28">
         <f>IF(F102="Pago",1,IF(G102=0,0.97,IF(G102&lt;=30,0.9,IF(G102&lt;=60,0.72,IF(G102&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -4757,8 +5376,8 @@
       <c r="A103" s="14" t="n"/>
       <c r="B103" s="14" t="n"/>
       <c r="C103" s="15" t="n"/>
-      <c r="D103" s="17" t="n"/>
-      <c r="E103" s="17" t="n"/>
+      <c r="D103" s="27" t="n"/>
+      <c r="E103" s="27" t="n"/>
       <c r="F103" s="14" t="n"/>
       <c r="G103" s="14">
         <f>IF(OR(F103="Pago",E103="",E103&gt;=TODAY()),0,TODAY()-E103)</f>
@@ -4768,7 +5387,7 @@
         <f>IF(F103="Pago","Pago",IF(G103=0,"A vencer",IF(G103&lt;=30,"1-30",IF(G103&lt;=60,"31-60",IF(G103&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I103" s="18">
+      <c r="I103" s="28">
         <f>IF(F103="Pago",1,IF(G103=0,0.97,IF(G103&lt;=30,0.9,IF(G103&lt;=60,0.72,IF(G103&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -4786,8 +5405,8 @@
       <c r="A104" s="14" t="n"/>
       <c r="B104" s="14" t="n"/>
       <c r="C104" s="15" t="n"/>
-      <c r="D104" s="17" t="n"/>
-      <c r="E104" s="17" t="n"/>
+      <c r="D104" s="27" t="n"/>
+      <c r="E104" s="27" t="n"/>
       <c r="F104" s="14" t="n"/>
       <c r="G104" s="14">
         <f>IF(OR(F104="Pago",E104="",E104&gt;=TODAY()),0,TODAY()-E104)</f>
@@ -4797,7 +5416,7 @@
         <f>IF(F104="Pago","Pago",IF(G104=0,"A vencer",IF(G104&lt;=30,"1-30",IF(G104&lt;=60,"31-60",IF(G104&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I104" s="18">
+      <c r="I104" s="28">
         <f>IF(F104="Pago",1,IF(G104=0,0.97,IF(G104&lt;=30,0.9,IF(G104&lt;=60,0.72,IF(G104&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -4815,8 +5434,8 @@
       <c r="A105" s="14" t="n"/>
       <c r="B105" s="14" t="n"/>
       <c r="C105" s="15" t="n"/>
-      <c r="D105" s="17" t="n"/>
-      <c r="E105" s="17" t="n"/>
+      <c r="D105" s="27" t="n"/>
+      <c r="E105" s="27" t="n"/>
       <c r="F105" s="14" t="n"/>
       <c r="G105" s="14">
         <f>IF(OR(F105="Pago",E105="",E105&gt;=TODAY()),0,TODAY()-E105)</f>
@@ -4826,7 +5445,7 @@
         <f>IF(F105="Pago","Pago",IF(G105=0,"A vencer",IF(G105&lt;=30,"1-30",IF(G105&lt;=60,"31-60",IF(G105&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I105" s="18">
+      <c r="I105" s="28">
         <f>IF(F105="Pago",1,IF(G105=0,0.97,IF(G105&lt;=30,0.9,IF(G105&lt;=60,0.72,IF(G105&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -4844,8 +5463,8 @@
       <c r="A106" s="14" t="n"/>
       <c r="B106" s="14" t="n"/>
       <c r="C106" s="15" t="n"/>
-      <c r="D106" s="17" t="n"/>
-      <c r="E106" s="17" t="n"/>
+      <c r="D106" s="27" t="n"/>
+      <c r="E106" s="27" t="n"/>
       <c r="F106" s="14" t="n"/>
       <c r="G106" s="14">
         <f>IF(OR(F106="Pago",E106="",E106&gt;=TODAY()),0,TODAY()-E106)</f>
@@ -4855,7 +5474,7 @@
         <f>IF(F106="Pago","Pago",IF(G106=0,"A vencer",IF(G106&lt;=30,"1-30",IF(G106&lt;=60,"31-60",IF(G106&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I106" s="18">
+      <c r="I106" s="28">
         <f>IF(F106="Pago",1,IF(G106=0,0.97,IF(G106&lt;=30,0.9,IF(G106&lt;=60,0.72,IF(G106&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -4873,8 +5492,8 @@
       <c r="A107" s="14" t="n"/>
       <c r="B107" s="14" t="n"/>
       <c r="C107" s="15" t="n"/>
-      <c r="D107" s="17" t="n"/>
-      <c r="E107" s="17" t="n"/>
+      <c r="D107" s="27" t="n"/>
+      <c r="E107" s="27" t="n"/>
       <c r="F107" s="14" t="n"/>
       <c r="G107" s="14">
         <f>IF(OR(F107="Pago",E107="",E107&gt;=TODAY()),0,TODAY()-E107)</f>
@@ -4884,7 +5503,7 @@
         <f>IF(F107="Pago","Pago",IF(G107=0,"A vencer",IF(G107&lt;=30,"1-30",IF(G107&lt;=60,"31-60",IF(G107&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I107" s="18">
+      <c r="I107" s="28">
         <f>IF(F107="Pago",1,IF(G107=0,0.97,IF(G107&lt;=30,0.9,IF(G107&lt;=60,0.72,IF(G107&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -4902,8 +5521,8 @@
       <c r="A108" s="14" t="n"/>
       <c r="B108" s="14" t="n"/>
       <c r="C108" s="15" t="n"/>
-      <c r="D108" s="17" t="n"/>
-      <c r="E108" s="17" t="n"/>
+      <c r="D108" s="27" t="n"/>
+      <c r="E108" s="27" t="n"/>
       <c r="F108" s="14" t="n"/>
       <c r="G108" s="14">
         <f>IF(OR(F108="Pago",E108="",E108&gt;=TODAY()),0,TODAY()-E108)</f>
@@ -4913,7 +5532,7 @@
         <f>IF(F108="Pago","Pago",IF(G108=0,"A vencer",IF(G108&lt;=30,"1-30",IF(G108&lt;=60,"31-60",IF(G108&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I108" s="18">
+      <c r="I108" s="28">
         <f>IF(F108="Pago",1,IF(G108=0,0.97,IF(G108&lt;=30,0.9,IF(G108&lt;=60,0.72,IF(G108&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -4931,8 +5550,8 @@
       <c r="A109" s="14" t="n"/>
       <c r="B109" s="14" t="n"/>
       <c r="C109" s="15" t="n"/>
-      <c r="D109" s="17" t="n"/>
-      <c r="E109" s="17" t="n"/>
+      <c r="D109" s="27" t="n"/>
+      <c r="E109" s="27" t="n"/>
       <c r="F109" s="14" t="n"/>
       <c r="G109" s="14">
         <f>IF(OR(F109="Pago",E109="",E109&gt;=TODAY()),0,TODAY()-E109)</f>
@@ -4942,7 +5561,7 @@
         <f>IF(F109="Pago","Pago",IF(G109=0,"A vencer",IF(G109&lt;=30,"1-30",IF(G109&lt;=60,"31-60",IF(G109&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I109" s="18">
+      <c r="I109" s="28">
         <f>IF(F109="Pago",1,IF(G109=0,0.97,IF(G109&lt;=30,0.9,IF(G109&lt;=60,0.72,IF(G109&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -4960,8 +5579,8 @@
       <c r="A110" s="14" t="n"/>
       <c r="B110" s="14" t="n"/>
       <c r="C110" s="15" t="n"/>
-      <c r="D110" s="17" t="n"/>
-      <c r="E110" s="17" t="n"/>
+      <c r="D110" s="27" t="n"/>
+      <c r="E110" s="27" t="n"/>
       <c r="F110" s="14" t="n"/>
       <c r="G110" s="14">
         <f>IF(OR(F110="Pago",E110="",E110&gt;=TODAY()),0,TODAY()-E110)</f>
@@ -4971,7 +5590,7 @@
         <f>IF(F110="Pago","Pago",IF(G110=0,"A vencer",IF(G110&lt;=30,"1-30",IF(G110&lt;=60,"31-60",IF(G110&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I110" s="18">
+      <c r="I110" s="28">
         <f>IF(F110="Pago",1,IF(G110=0,0.97,IF(G110&lt;=30,0.9,IF(G110&lt;=60,0.72,IF(G110&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -4989,8 +5608,8 @@
       <c r="A111" s="14" t="n"/>
       <c r="B111" s="14" t="n"/>
       <c r="C111" s="15" t="n"/>
-      <c r="D111" s="17" t="n"/>
-      <c r="E111" s="17" t="n"/>
+      <c r="D111" s="27" t="n"/>
+      <c r="E111" s="27" t="n"/>
       <c r="F111" s="14" t="n"/>
       <c r="G111" s="14">
         <f>IF(OR(F111="Pago",E111="",E111&gt;=TODAY()),0,TODAY()-E111)</f>
@@ -5000,7 +5619,7 @@
         <f>IF(F111="Pago","Pago",IF(G111=0,"A vencer",IF(G111&lt;=30,"1-30",IF(G111&lt;=60,"31-60",IF(G111&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I111" s="18">
+      <c r="I111" s="28">
         <f>IF(F111="Pago",1,IF(G111=0,0.97,IF(G111&lt;=30,0.9,IF(G111&lt;=60,0.72,IF(G111&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -5018,8 +5637,8 @@
       <c r="A112" s="14" t="n"/>
       <c r="B112" s="14" t="n"/>
       <c r="C112" s="15" t="n"/>
-      <c r="D112" s="17" t="n"/>
-      <c r="E112" s="17" t="n"/>
+      <c r="D112" s="27" t="n"/>
+      <c r="E112" s="27" t="n"/>
       <c r="F112" s="14" t="n"/>
       <c r="G112" s="14">
         <f>IF(OR(F112="Pago",E112="",E112&gt;=TODAY()),0,TODAY()-E112)</f>
@@ -5029,7 +5648,7 @@
         <f>IF(F112="Pago","Pago",IF(G112=0,"A vencer",IF(G112&lt;=30,"1-30",IF(G112&lt;=60,"31-60",IF(G112&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I112" s="18">
+      <c r="I112" s="28">
         <f>IF(F112="Pago",1,IF(G112=0,0.97,IF(G112&lt;=30,0.9,IF(G112&lt;=60,0.72,IF(G112&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -5047,8 +5666,8 @@
       <c r="A113" s="14" t="n"/>
       <c r="B113" s="14" t="n"/>
       <c r="C113" s="15" t="n"/>
-      <c r="D113" s="17" t="n"/>
-      <c r="E113" s="17" t="n"/>
+      <c r="D113" s="27" t="n"/>
+      <c r="E113" s="27" t="n"/>
       <c r="F113" s="14" t="n"/>
       <c r="G113" s="14">
         <f>IF(OR(F113="Pago",E113="",E113&gt;=TODAY()),0,TODAY()-E113)</f>
@@ -5058,7 +5677,7 @@
         <f>IF(F113="Pago","Pago",IF(G113=0,"A vencer",IF(G113&lt;=30,"1-30",IF(G113&lt;=60,"31-60",IF(G113&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I113" s="18">
+      <c r="I113" s="28">
         <f>IF(F113="Pago",1,IF(G113=0,0.97,IF(G113&lt;=30,0.9,IF(G113&lt;=60,0.72,IF(G113&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -5076,8 +5695,8 @@
       <c r="A114" s="14" t="n"/>
       <c r="B114" s="14" t="n"/>
       <c r="C114" s="15" t="n"/>
-      <c r="D114" s="17" t="n"/>
-      <c r="E114" s="17" t="n"/>
+      <c r="D114" s="27" t="n"/>
+      <c r="E114" s="27" t="n"/>
       <c r="F114" s="14" t="n"/>
       <c r="G114" s="14">
         <f>IF(OR(F114="Pago",E114="",E114&gt;=TODAY()),0,TODAY()-E114)</f>
@@ -5087,7 +5706,7 @@
         <f>IF(F114="Pago","Pago",IF(G114=0,"A vencer",IF(G114&lt;=30,"1-30",IF(G114&lt;=60,"31-60",IF(G114&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I114" s="18">
+      <c r="I114" s="28">
         <f>IF(F114="Pago",1,IF(G114=0,0.97,IF(G114&lt;=30,0.9,IF(G114&lt;=60,0.72,IF(G114&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -5105,8 +5724,8 @@
       <c r="A115" s="14" t="n"/>
       <c r="B115" s="14" t="n"/>
       <c r="C115" s="15" t="n"/>
-      <c r="D115" s="17" t="n"/>
-      <c r="E115" s="17" t="n"/>
+      <c r="D115" s="27" t="n"/>
+      <c r="E115" s="27" t="n"/>
       <c r="F115" s="14" t="n"/>
       <c r="G115" s="14">
         <f>IF(OR(F115="Pago",E115="",E115&gt;=TODAY()),0,TODAY()-E115)</f>
@@ -5116,7 +5735,7 @@
         <f>IF(F115="Pago","Pago",IF(G115=0,"A vencer",IF(G115&lt;=30,"1-30",IF(G115&lt;=60,"31-60",IF(G115&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I115" s="18">
+      <c r="I115" s="28">
         <f>IF(F115="Pago",1,IF(G115=0,0.97,IF(G115&lt;=30,0.9,IF(G115&lt;=60,0.72,IF(G115&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -5134,8 +5753,8 @@
       <c r="A116" s="14" t="n"/>
       <c r="B116" s="14" t="n"/>
       <c r="C116" s="15" t="n"/>
-      <c r="D116" s="17" t="n"/>
-      <c r="E116" s="17" t="n"/>
+      <c r="D116" s="27" t="n"/>
+      <c r="E116" s="27" t="n"/>
       <c r="F116" s="14" t="n"/>
       <c r="G116" s="14">
         <f>IF(OR(F116="Pago",E116="",E116&gt;=TODAY()),0,TODAY()-E116)</f>
@@ -5145,7 +5764,7 @@
         <f>IF(F116="Pago","Pago",IF(G116=0,"A vencer",IF(G116&lt;=30,"1-30",IF(G116&lt;=60,"31-60",IF(G116&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I116" s="18">
+      <c r="I116" s="28">
         <f>IF(F116="Pago",1,IF(G116=0,0.97,IF(G116&lt;=30,0.9,IF(G116&lt;=60,0.72,IF(G116&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -5163,8 +5782,8 @@
       <c r="A117" s="14" t="n"/>
       <c r="B117" s="14" t="n"/>
       <c r="C117" s="15" t="n"/>
-      <c r="D117" s="17" t="n"/>
-      <c r="E117" s="17" t="n"/>
+      <c r="D117" s="27" t="n"/>
+      <c r="E117" s="27" t="n"/>
       <c r="F117" s="14" t="n"/>
       <c r="G117" s="14">
         <f>IF(OR(F117="Pago",E117="",E117&gt;=TODAY()),0,TODAY()-E117)</f>
@@ -5174,7 +5793,7 @@
         <f>IF(F117="Pago","Pago",IF(G117=0,"A vencer",IF(G117&lt;=30,"1-30",IF(G117&lt;=60,"31-60",IF(G117&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I117" s="18">
+      <c r="I117" s="28">
         <f>IF(F117="Pago",1,IF(G117=0,0.97,IF(G117&lt;=30,0.9,IF(G117&lt;=60,0.72,IF(G117&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -5192,8 +5811,8 @@
       <c r="A118" s="14" t="n"/>
       <c r="B118" s="14" t="n"/>
       <c r="C118" s="15" t="n"/>
-      <c r="D118" s="17" t="n"/>
-      <c r="E118" s="17" t="n"/>
+      <c r="D118" s="27" t="n"/>
+      <c r="E118" s="27" t="n"/>
       <c r="F118" s="14" t="n"/>
       <c r="G118" s="14">
         <f>IF(OR(F118="Pago",E118="",E118&gt;=TODAY()),0,TODAY()-E118)</f>
@@ -5203,7 +5822,7 @@
         <f>IF(F118="Pago","Pago",IF(G118=0,"A vencer",IF(G118&lt;=30,"1-30",IF(G118&lt;=60,"31-60",IF(G118&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I118" s="18">
+      <c r="I118" s="28">
         <f>IF(F118="Pago",1,IF(G118=0,0.97,IF(G118&lt;=30,0.9,IF(G118&lt;=60,0.72,IF(G118&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -5221,8 +5840,8 @@
       <c r="A119" s="14" t="n"/>
       <c r="B119" s="14" t="n"/>
       <c r="C119" s="15" t="n"/>
-      <c r="D119" s="17" t="n"/>
-      <c r="E119" s="17" t="n"/>
+      <c r="D119" s="27" t="n"/>
+      <c r="E119" s="27" t="n"/>
       <c r="F119" s="14" t="n"/>
       <c r="G119" s="14">
         <f>IF(OR(F119="Pago",E119="",E119&gt;=TODAY()),0,TODAY()-E119)</f>
@@ -5232,7 +5851,7 @@
         <f>IF(F119="Pago","Pago",IF(G119=0,"A vencer",IF(G119&lt;=30,"1-30",IF(G119&lt;=60,"31-60",IF(G119&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I119" s="18">
+      <c r="I119" s="28">
         <f>IF(F119="Pago",1,IF(G119=0,0.97,IF(G119&lt;=30,0.9,IF(G119&lt;=60,0.72,IF(G119&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -5250,8 +5869,8 @@
       <c r="A120" s="14" t="n"/>
       <c r="B120" s="14" t="n"/>
       <c r="C120" s="15" t="n"/>
-      <c r="D120" s="17" t="n"/>
-      <c r="E120" s="17" t="n"/>
+      <c r="D120" s="27" t="n"/>
+      <c r="E120" s="27" t="n"/>
       <c r="F120" s="14" t="n"/>
       <c r="G120" s="14">
         <f>IF(OR(F120="Pago",E120="",E120&gt;=TODAY()),0,TODAY()-E120)</f>
@@ -5261,7 +5880,7 @@
         <f>IF(F120="Pago","Pago",IF(G120=0,"A vencer",IF(G120&lt;=30,"1-30",IF(G120&lt;=60,"31-60",IF(G120&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I120" s="18">
+      <c r="I120" s="28">
         <f>IF(F120="Pago",1,IF(G120=0,0.97,IF(G120&lt;=30,0.9,IF(G120&lt;=60,0.72,IF(G120&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -5279,8 +5898,8 @@
       <c r="A121" s="14" t="n"/>
       <c r="B121" s="14" t="n"/>
       <c r="C121" s="15" t="n"/>
-      <c r="D121" s="17" t="n"/>
-      <c r="E121" s="17" t="n"/>
+      <c r="D121" s="27" t="n"/>
+      <c r="E121" s="27" t="n"/>
       <c r="F121" s="14" t="n"/>
       <c r="G121" s="14">
         <f>IF(OR(F121="Pago",E121="",E121&gt;=TODAY()),0,TODAY()-E121)</f>
@@ -5290,7 +5909,7 @@
         <f>IF(F121="Pago","Pago",IF(G121=0,"A vencer",IF(G121&lt;=30,"1-30",IF(G121&lt;=60,"31-60",IF(G121&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I121" s="18">
+      <c r="I121" s="28">
         <f>IF(F121="Pago",1,IF(G121=0,0.97,IF(G121&lt;=30,0.9,IF(G121&lt;=60,0.72,IF(G121&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -5308,8 +5927,8 @@
       <c r="A122" s="14" t="n"/>
       <c r="B122" s="14" t="n"/>
       <c r="C122" s="15" t="n"/>
-      <c r="D122" s="17" t="n"/>
-      <c r="E122" s="17" t="n"/>
+      <c r="D122" s="27" t="n"/>
+      <c r="E122" s="27" t="n"/>
       <c r="F122" s="14" t="n"/>
       <c r="G122" s="14">
         <f>IF(OR(F122="Pago",E122="",E122&gt;=TODAY()),0,TODAY()-E122)</f>
@@ -5319,7 +5938,7 @@
         <f>IF(F122="Pago","Pago",IF(G122=0,"A vencer",IF(G122&lt;=30,"1-30",IF(G122&lt;=60,"31-60",IF(G122&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I122" s="18">
+      <c r="I122" s="28">
         <f>IF(F122="Pago",1,IF(G122=0,0.97,IF(G122&lt;=30,0.9,IF(G122&lt;=60,0.72,IF(G122&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -5337,8 +5956,8 @@
       <c r="A123" s="14" t="n"/>
       <c r="B123" s="14" t="n"/>
       <c r="C123" s="15" t="n"/>
-      <c r="D123" s="17" t="n"/>
-      <c r="E123" s="17" t="n"/>
+      <c r="D123" s="27" t="n"/>
+      <c r="E123" s="27" t="n"/>
       <c r="F123" s="14" t="n"/>
       <c r="G123" s="14">
         <f>IF(OR(F123="Pago",E123="",E123&gt;=TODAY()),0,TODAY()-E123)</f>
@@ -5348,7 +5967,7 @@
         <f>IF(F123="Pago","Pago",IF(G123=0,"A vencer",IF(G123&lt;=30,"1-30",IF(G123&lt;=60,"31-60",IF(G123&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I123" s="18">
+      <c r="I123" s="28">
         <f>IF(F123="Pago",1,IF(G123=0,0.97,IF(G123&lt;=30,0.9,IF(G123&lt;=60,0.72,IF(G123&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -5366,8 +5985,8 @@
       <c r="A124" s="14" t="n"/>
       <c r="B124" s="14" t="n"/>
       <c r="C124" s="15" t="n"/>
-      <c r="D124" s="17" t="n"/>
-      <c r="E124" s="17" t="n"/>
+      <c r="D124" s="27" t="n"/>
+      <c r="E124" s="27" t="n"/>
       <c r="F124" s="14" t="n"/>
       <c r="G124" s="14">
         <f>IF(OR(F124="Pago",E124="",E124&gt;=TODAY()),0,TODAY()-E124)</f>
@@ -5377,7 +5996,7 @@
         <f>IF(F124="Pago","Pago",IF(G124=0,"A vencer",IF(G124&lt;=30,"1-30",IF(G124&lt;=60,"31-60",IF(G124&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I124" s="18">
+      <c r="I124" s="28">
         <f>IF(F124="Pago",1,IF(G124=0,0.97,IF(G124&lt;=30,0.9,IF(G124&lt;=60,0.72,IF(G124&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -5395,8 +6014,8 @@
       <c r="A125" s="14" t="n"/>
       <c r="B125" s="14" t="n"/>
       <c r="C125" s="15" t="n"/>
-      <c r="D125" s="17" t="n"/>
-      <c r="E125" s="17" t="n"/>
+      <c r="D125" s="27" t="n"/>
+      <c r="E125" s="27" t="n"/>
       <c r="F125" s="14" t="n"/>
       <c r="G125" s="14">
         <f>IF(OR(F125="Pago",E125="",E125&gt;=TODAY()),0,TODAY()-E125)</f>
@@ -5406,7 +6025,7 @@
         <f>IF(F125="Pago","Pago",IF(G125=0,"A vencer",IF(G125&lt;=30,"1-30",IF(G125&lt;=60,"31-60",IF(G125&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I125" s="18">
+      <c r="I125" s="28">
         <f>IF(F125="Pago",1,IF(G125=0,0.97,IF(G125&lt;=30,0.9,IF(G125&lt;=60,0.72,IF(G125&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -5424,8 +6043,8 @@
       <c r="A126" s="14" t="n"/>
       <c r="B126" s="14" t="n"/>
       <c r="C126" s="15" t="n"/>
-      <c r="D126" s="17" t="n"/>
-      <c r="E126" s="17" t="n"/>
+      <c r="D126" s="27" t="n"/>
+      <c r="E126" s="27" t="n"/>
       <c r="F126" s="14" t="n"/>
       <c r="G126" s="14">
         <f>IF(OR(F126="Pago",E126="",E126&gt;=TODAY()),0,TODAY()-E126)</f>
@@ -5435,7 +6054,7 @@
         <f>IF(F126="Pago","Pago",IF(G126=0,"A vencer",IF(G126&lt;=30,"1-30",IF(G126&lt;=60,"31-60",IF(G126&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I126" s="18">
+      <c r="I126" s="28">
         <f>IF(F126="Pago",1,IF(G126=0,0.97,IF(G126&lt;=30,0.9,IF(G126&lt;=60,0.72,IF(G126&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -5453,8 +6072,8 @@
       <c r="A127" s="14" t="n"/>
       <c r="B127" s="14" t="n"/>
       <c r="C127" s="15" t="n"/>
-      <c r="D127" s="17" t="n"/>
-      <c r="E127" s="17" t="n"/>
+      <c r="D127" s="27" t="n"/>
+      <c r="E127" s="27" t="n"/>
       <c r="F127" s="14" t="n"/>
       <c r="G127" s="14">
         <f>IF(OR(F127="Pago",E127="",E127&gt;=TODAY()),0,TODAY()-E127)</f>
@@ -5464,7 +6083,7 @@
         <f>IF(F127="Pago","Pago",IF(G127=0,"A vencer",IF(G127&lt;=30,"1-30",IF(G127&lt;=60,"31-60",IF(G127&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I127" s="18">
+      <c r="I127" s="28">
         <f>IF(F127="Pago",1,IF(G127=0,0.97,IF(G127&lt;=30,0.9,IF(G127&lt;=60,0.72,IF(G127&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -5482,8 +6101,8 @@
       <c r="A128" s="14" t="n"/>
       <c r="B128" s="14" t="n"/>
       <c r="C128" s="15" t="n"/>
-      <c r="D128" s="17" t="n"/>
-      <c r="E128" s="17" t="n"/>
+      <c r="D128" s="27" t="n"/>
+      <c r="E128" s="27" t="n"/>
       <c r="F128" s="14" t="n"/>
       <c r="G128" s="14">
         <f>IF(OR(F128="Pago",E128="",E128&gt;=TODAY()),0,TODAY()-E128)</f>
@@ -5493,7 +6112,7 @@
         <f>IF(F128="Pago","Pago",IF(G128=0,"A vencer",IF(G128&lt;=30,"1-30",IF(G128&lt;=60,"31-60",IF(G128&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I128" s="18">
+      <c r="I128" s="28">
         <f>IF(F128="Pago",1,IF(G128=0,0.97,IF(G128&lt;=30,0.9,IF(G128&lt;=60,0.72,IF(G128&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -5511,8 +6130,8 @@
       <c r="A129" s="14" t="n"/>
       <c r="B129" s="14" t="n"/>
       <c r="C129" s="15" t="n"/>
-      <c r="D129" s="17" t="n"/>
-      <c r="E129" s="17" t="n"/>
+      <c r="D129" s="27" t="n"/>
+      <c r="E129" s="27" t="n"/>
       <c r="F129" s="14" t="n"/>
       <c r="G129" s="14">
         <f>IF(OR(F129="Pago",E129="",E129&gt;=TODAY()),0,TODAY()-E129)</f>
@@ -5522,7 +6141,7 @@
         <f>IF(F129="Pago","Pago",IF(G129=0,"A vencer",IF(G129&lt;=30,"1-30",IF(G129&lt;=60,"31-60",IF(G129&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I129" s="18">
+      <c r="I129" s="28">
         <f>IF(F129="Pago",1,IF(G129=0,0.97,IF(G129&lt;=30,0.9,IF(G129&lt;=60,0.72,IF(G129&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -5540,8 +6159,8 @@
       <c r="A130" s="14" t="n"/>
       <c r="B130" s="14" t="n"/>
       <c r="C130" s="15" t="n"/>
-      <c r="D130" s="17" t="n"/>
-      <c r="E130" s="17" t="n"/>
+      <c r="D130" s="27" t="n"/>
+      <c r="E130" s="27" t="n"/>
       <c r="F130" s="14" t="n"/>
       <c r="G130" s="14">
         <f>IF(OR(F130="Pago",E130="",E130&gt;=TODAY()),0,TODAY()-E130)</f>
@@ -5551,7 +6170,7 @@
         <f>IF(F130="Pago","Pago",IF(G130=0,"A vencer",IF(G130&lt;=30,"1-30",IF(G130&lt;=60,"31-60",IF(G130&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I130" s="18">
+      <c r="I130" s="28">
         <f>IF(F130="Pago",1,IF(G130=0,0.97,IF(G130&lt;=30,0.9,IF(G130&lt;=60,0.72,IF(G130&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -5569,8 +6188,8 @@
       <c r="A131" s="14" t="n"/>
       <c r="B131" s="14" t="n"/>
       <c r="C131" s="15" t="n"/>
-      <c r="D131" s="17" t="n"/>
-      <c r="E131" s="17" t="n"/>
+      <c r="D131" s="27" t="n"/>
+      <c r="E131" s="27" t="n"/>
       <c r="F131" s="14" t="n"/>
       <c r="G131" s="14">
         <f>IF(OR(F131="Pago",E131="",E131&gt;=TODAY()),0,TODAY()-E131)</f>
@@ -5580,7 +6199,7 @@
         <f>IF(F131="Pago","Pago",IF(G131=0,"A vencer",IF(G131&lt;=30,"1-30",IF(G131&lt;=60,"31-60",IF(G131&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I131" s="18">
+      <c r="I131" s="28">
         <f>IF(F131="Pago",1,IF(G131=0,0.97,IF(G131&lt;=30,0.9,IF(G131&lt;=60,0.72,IF(G131&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -5598,8 +6217,8 @@
       <c r="A132" s="14" t="n"/>
       <c r="B132" s="14" t="n"/>
       <c r="C132" s="15" t="n"/>
-      <c r="D132" s="17" t="n"/>
-      <c r="E132" s="17" t="n"/>
+      <c r="D132" s="27" t="n"/>
+      <c r="E132" s="27" t="n"/>
       <c r="F132" s="14" t="n"/>
       <c r="G132" s="14">
         <f>IF(OR(F132="Pago",E132="",E132&gt;=TODAY()),0,TODAY()-E132)</f>
@@ -5609,7 +6228,7 @@
         <f>IF(F132="Pago","Pago",IF(G132=0,"A vencer",IF(G132&lt;=30,"1-30",IF(G132&lt;=60,"31-60",IF(G132&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I132" s="18">
+      <c r="I132" s="28">
         <f>IF(F132="Pago",1,IF(G132=0,0.97,IF(G132&lt;=30,0.9,IF(G132&lt;=60,0.72,IF(G132&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -5627,8 +6246,8 @@
       <c r="A133" s="14" t="n"/>
       <c r="B133" s="14" t="n"/>
       <c r="C133" s="15" t="n"/>
-      <c r="D133" s="17" t="n"/>
-      <c r="E133" s="17" t="n"/>
+      <c r="D133" s="27" t="n"/>
+      <c r="E133" s="27" t="n"/>
       <c r="F133" s="14" t="n"/>
       <c r="G133" s="14">
         <f>IF(OR(F133="Pago",E133="",E133&gt;=TODAY()),0,TODAY()-E133)</f>
@@ -5638,7 +6257,7 @@
         <f>IF(F133="Pago","Pago",IF(G133=0,"A vencer",IF(G133&lt;=30,"1-30",IF(G133&lt;=60,"31-60",IF(G133&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I133" s="18">
+      <c r="I133" s="28">
         <f>IF(F133="Pago",1,IF(G133=0,0.97,IF(G133&lt;=30,0.9,IF(G133&lt;=60,0.72,IF(G133&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -5656,8 +6275,8 @@
       <c r="A134" s="14" t="n"/>
       <c r="B134" s="14" t="n"/>
       <c r="C134" s="15" t="n"/>
-      <c r="D134" s="17" t="n"/>
-      <c r="E134" s="17" t="n"/>
+      <c r="D134" s="27" t="n"/>
+      <c r="E134" s="27" t="n"/>
       <c r="F134" s="14" t="n"/>
       <c r="G134" s="14">
         <f>IF(OR(F134="Pago",E134="",E134&gt;=TODAY()),0,TODAY()-E134)</f>
@@ -5667,7 +6286,7 @@
         <f>IF(F134="Pago","Pago",IF(G134=0,"A vencer",IF(G134&lt;=30,"1-30",IF(G134&lt;=60,"31-60",IF(G134&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I134" s="18">
+      <c r="I134" s="28">
         <f>IF(F134="Pago",1,IF(G134=0,0.97,IF(G134&lt;=30,0.9,IF(G134&lt;=60,0.72,IF(G134&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -5685,8 +6304,8 @@
       <c r="A135" s="14" t="n"/>
       <c r="B135" s="14" t="n"/>
       <c r="C135" s="15" t="n"/>
-      <c r="D135" s="17" t="n"/>
-      <c r="E135" s="17" t="n"/>
+      <c r="D135" s="27" t="n"/>
+      <c r="E135" s="27" t="n"/>
       <c r="F135" s="14" t="n"/>
       <c r="G135" s="14">
         <f>IF(OR(F135="Pago",E135="",E135&gt;=TODAY()),0,TODAY()-E135)</f>
@@ -5696,7 +6315,7 @@
         <f>IF(F135="Pago","Pago",IF(G135=0,"A vencer",IF(G135&lt;=30,"1-30",IF(G135&lt;=60,"31-60",IF(G135&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I135" s="18">
+      <c r="I135" s="28">
         <f>IF(F135="Pago",1,IF(G135=0,0.97,IF(G135&lt;=30,0.9,IF(G135&lt;=60,0.72,IF(G135&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -5714,8 +6333,8 @@
       <c r="A136" s="14" t="n"/>
       <c r="B136" s="14" t="n"/>
       <c r="C136" s="15" t="n"/>
-      <c r="D136" s="17" t="n"/>
-      <c r="E136" s="17" t="n"/>
+      <c r="D136" s="27" t="n"/>
+      <c r="E136" s="27" t="n"/>
       <c r="F136" s="14" t="n"/>
       <c r="G136" s="14">
         <f>IF(OR(F136="Pago",E136="",E136&gt;=TODAY()),0,TODAY()-E136)</f>
@@ -5725,7 +6344,7 @@
         <f>IF(F136="Pago","Pago",IF(G136=0,"A vencer",IF(G136&lt;=30,"1-30",IF(G136&lt;=60,"31-60",IF(G136&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I136" s="18">
+      <c r="I136" s="28">
         <f>IF(F136="Pago",1,IF(G136=0,0.97,IF(G136&lt;=30,0.9,IF(G136&lt;=60,0.72,IF(G136&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -5743,8 +6362,8 @@
       <c r="A137" s="14" t="n"/>
       <c r="B137" s="14" t="n"/>
       <c r="C137" s="15" t="n"/>
-      <c r="D137" s="17" t="n"/>
-      <c r="E137" s="17" t="n"/>
+      <c r="D137" s="27" t="n"/>
+      <c r="E137" s="27" t="n"/>
       <c r="F137" s="14" t="n"/>
       <c r="G137" s="14">
         <f>IF(OR(F137="Pago",E137="",E137&gt;=TODAY()),0,TODAY()-E137)</f>
@@ -5754,7 +6373,7 @@
         <f>IF(F137="Pago","Pago",IF(G137=0,"A vencer",IF(G137&lt;=30,"1-30",IF(G137&lt;=60,"31-60",IF(G137&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I137" s="18">
+      <c r="I137" s="28">
         <f>IF(F137="Pago",1,IF(G137=0,0.97,IF(G137&lt;=30,0.9,IF(G137&lt;=60,0.72,IF(G137&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -5772,8 +6391,8 @@
       <c r="A138" s="14" t="n"/>
       <c r="B138" s="14" t="n"/>
       <c r="C138" s="15" t="n"/>
-      <c r="D138" s="17" t="n"/>
-      <c r="E138" s="17" t="n"/>
+      <c r="D138" s="27" t="n"/>
+      <c r="E138" s="27" t="n"/>
       <c r="F138" s="14" t="n"/>
       <c r="G138" s="14">
         <f>IF(OR(F138="Pago",E138="",E138&gt;=TODAY()),0,TODAY()-E138)</f>
@@ -5783,7 +6402,7 @@
         <f>IF(F138="Pago","Pago",IF(G138=0,"A vencer",IF(G138&lt;=30,"1-30",IF(G138&lt;=60,"31-60",IF(G138&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I138" s="18">
+      <c r="I138" s="28">
         <f>IF(F138="Pago",1,IF(G138=0,0.97,IF(G138&lt;=30,0.9,IF(G138&lt;=60,0.72,IF(G138&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -5801,8 +6420,8 @@
       <c r="A139" s="14" t="n"/>
       <c r="B139" s="14" t="n"/>
       <c r="C139" s="15" t="n"/>
-      <c r="D139" s="17" t="n"/>
-      <c r="E139" s="17" t="n"/>
+      <c r="D139" s="27" t="n"/>
+      <c r="E139" s="27" t="n"/>
       <c r="F139" s="14" t="n"/>
       <c r="G139" s="14">
         <f>IF(OR(F139="Pago",E139="",E139&gt;=TODAY()),0,TODAY()-E139)</f>
@@ -5812,7 +6431,7 @@
         <f>IF(F139="Pago","Pago",IF(G139=0,"A vencer",IF(G139&lt;=30,"1-30",IF(G139&lt;=60,"31-60",IF(G139&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I139" s="18">
+      <c r="I139" s="28">
         <f>IF(F139="Pago",1,IF(G139=0,0.97,IF(G139&lt;=30,0.9,IF(G139&lt;=60,0.72,IF(G139&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -5830,8 +6449,8 @@
       <c r="A140" s="14" t="n"/>
       <c r="B140" s="14" t="n"/>
       <c r="C140" s="15" t="n"/>
-      <c r="D140" s="17" t="n"/>
-      <c r="E140" s="17" t="n"/>
+      <c r="D140" s="27" t="n"/>
+      <c r="E140" s="27" t="n"/>
       <c r="F140" s="14" t="n"/>
       <c r="G140" s="14">
         <f>IF(OR(F140="Pago",E140="",E140&gt;=TODAY()),0,TODAY()-E140)</f>
@@ -5841,7 +6460,7 @@
         <f>IF(F140="Pago","Pago",IF(G140=0,"A vencer",IF(G140&lt;=30,"1-30",IF(G140&lt;=60,"31-60",IF(G140&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I140" s="18">
+      <c r="I140" s="28">
         <f>IF(F140="Pago",1,IF(G140=0,0.97,IF(G140&lt;=30,0.9,IF(G140&lt;=60,0.72,IF(G140&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -5859,8 +6478,8 @@
       <c r="A141" s="14" t="n"/>
       <c r="B141" s="14" t="n"/>
       <c r="C141" s="15" t="n"/>
-      <c r="D141" s="17" t="n"/>
-      <c r="E141" s="17" t="n"/>
+      <c r="D141" s="27" t="n"/>
+      <c r="E141" s="27" t="n"/>
       <c r="F141" s="14" t="n"/>
       <c r="G141" s="14">
         <f>IF(OR(F141="Pago",E141="",E141&gt;=TODAY()),0,TODAY()-E141)</f>
@@ -5870,7 +6489,7 @@
         <f>IF(F141="Pago","Pago",IF(G141=0,"A vencer",IF(G141&lt;=30,"1-30",IF(G141&lt;=60,"31-60",IF(G141&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I141" s="18">
+      <c r="I141" s="28">
         <f>IF(F141="Pago",1,IF(G141=0,0.97,IF(G141&lt;=30,0.9,IF(G141&lt;=60,0.72,IF(G141&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -5888,8 +6507,8 @@
       <c r="A142" s="14" t="n"/>
       <c r="B142" s="14" t="n"/>
       <c r="C142" s="15" t="n"/>
-      <c r="D142" s="17" t="n"/>
-      <c r="E142" s="17" t="n"/>
+      <c r="D142" s="27" t="n"/>
+      <c r="E142" s="27" t="n"/>
       <c r="F142" s="14" t="n"/>
       <c r="G142" s="14">
         <f>IF(OR(F142="Pago",E142="",E142&gt;=TODAY()),0,TODAY()-E142)</f>
@@ -5899,7 +6518,7 @@
         <f>IF(F142="Pago","Pago",IF(G142=0,"A vencer",IF(G142&lt;=30,"1-30",IF(G142&lt;=60,"31-60",IF(G142&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I142" s="18">
+      <c r="I142" s="28">
         <f>IF(F142="Pago",1,IF(G142=0,0.97,IF(G142&lt;=30,0.9,IF(G142&lt;=60,0.72,IF(G142&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -5917,8 +6536,8 @@
       <c r="A143" s="14" t="n"/>
       <c r="B143" s="14" t="n"/>
       <c r="C143" s="15" t="n"/>
-      <c r="D143" s="17" t="n"/>
-      <c r="E143" s="17" t="n"/>
+      <c r="D143" s="27" t="n"/>
+      <c r="E143" s="27" t="n"/>
       <c r="F143" s="14" t="n"/>
       <c r="G143" s="14">
         <f>IF(OR(F143="Pago",E143="",E143&gt;=TODAY()),0,TODAY()-E143)</f>
@@ -5928,7 +6547,7 @@
         <f>IF(F143="Pago","Pago",IF(G143=0,"A vencer",IF(G143&lt;=30,"1-30",IF(G143&lt;=60,"31-60",IF(G143&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I143" s="18">
+      <c r="I143" s="28">
         <f>IF(F143="Pago",1,IF(G143=0,0.97,IF(G143&lt;=30,0.9,IF(G143&lt;=60,0.72,IF(G143&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -5946,8 +6565,8 @@
       <c r="A144" s="14" t="n"/>
       <c r="B144" s="14" t="n"/>
       <c r="C144" s="15" t="n"/>
-      <c r="D144" s="17" t="n"/>
-      <c r="E144" s="17" t="n"/>
+      <c r="D144" s="27" t="n"/>
+      <c r="E144" s="27" t="n"/>
       <c r="F144" s="14" t="n"/>
       <c r="G144" s="14">
         <f>IF(OR(F144="Pago",E144="",E144&gt;=TODAY()),0,TODAY()-E144)</f>
@@ -5957,7 +6576,7 @@
         <f>IF(F144="Pago","Pago",IF(G144=0,"A vencer",IF(G144&lt;=30,"1-30",IF(G144&lt;=60,"31-60",IF(G144&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I144" s="18">
+      <c r="I144" s="28">
         <f>IF(F144="Pago",1,IF(G144=0,0.97,IF(G144&lt;=30,0.9,IF(G144&lt;=60,0.72,IF(G144&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -5975,8 +6594,8 @@
       <c r="A145" s="14" t="n"/>
       <c r="B145" s="14" t="n"/>
       <c r="C145" s="15" t="n"/>
-      <c r="D145" s="17" t="n"/>
-      <c r="E145" s="17" t="n"/>
+      <c r="D145" s="27" t="n"/>
+      <c r="E145" s="27" t="n"/>
       <c r="F145" s="14" t="n"/>
       <c r="G145" s="14">
         <f>IF(OR(F145="Pago",E145="",E145&gt;=TODAY()),0,TODAY()-E145)</f>
@@ -5986,7 +6605,7 @@
         <f>IF(F145="Pago","Pago",IF(G145=0,"A vencer",IF(G145&lt;=30,"1-30",IF(G145&lt;=60,"31-60",IF(G145&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I145" s="18">
+      <c r="I145" s="28">
         <f>IF(F145="Pago",1,IF(G145=0,0.97,IF(G145&lt;=30,0.9,IF(G145&lt;=60,0.72,IF(G145&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -6004,8 +6623,8 @@
       <c r="A146" s="14" t="n"/>
       <c r="B146" s="14" t="n"/>
       <c r="C146" s="15" t="n"/>
-      <c r="D146" s="17" t="n"/>
-      <c r="E146" s="17" t="n"/>
+      <c r="D146" s="27" t="n"/>
+      <c r="E146" s="27" t="n"/>
       <c r="F146" s="14" t="n"/>
       <c r="G146" s="14">
         <f>IF(OR(F146="Pago",E146="",E146&gt;=TODAY()),0,TODAY()-E146)</f>
@@ -6015,7 +6634,7 @@
         <f>IF(F146="Pago","Pago",IF(G146=0,"A vencer",IF(G146&lt;=30,"1-30",IF(G146&lt;=60,"31-60",IF(G146&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I146" s="18">
+      <c r="I146" s="28">
         <f>IF(F146="Pago",1,IF(G146=0,0.97,IF(G146&lt;=30,0.9,IF(G146&lt;=60,0.72,IF(G146&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -6033,8 +6652,8 @@
       <c r="A147" s="14" t="n"/>
       <c r="B147" s="14" t="n"/>
       <c r="C147" s="15" t="n"/>
-      <c r="D147" s="17" t="n"/>
-      <c r="E147" s="17" t="n"/>
+      <c r="D147" s="27" t="n"/>
+      <c r="E147" s="27" t="n"/>
       <c r="F147" s="14" t="n"/>
       <c r="G147" s="14">
         <f>IF(OR(F147="Pago",E147="",E147&gt;=TODAY()),0,TODAY()-E147)</f>
@@ -6044,7 +6663,7 @@
         <f>IF(F147="Pago","Pago",IF(G147=0,"A vencer",IF(G147&lt;=30,"1-30",IF(G147&lt;=60,"31-60",IF(G147&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I147" s="18">
+      <c r="I147" s="28">
         <f>IF(F147="Pago",1,IF(G147=0,0.97,IF(G147&lt;=30,0.9,IF(G147&lt;=60,0.72,IF(G147&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -6062,8 +6681,8 @@
       <c r="A148" s="14" t="n"/>
       <c r="B148" s="14" t="n"/>
       <c r="C148" s="15" t="n"/>
-      <c r="D148" s="17" t="n"/>
-      <c r="E148" s="17" t="n"/>
+      <c r="D148" s="27" t="n"/>
+      <c r="E148" s="27" t="n"/>
       <c r="F148" s="14" t="n"/>
       <c r="G148" s="14">
         <f>IF(OR(F148="Pago",E148="",E148&gt;=TODAY()),0,TODAY()-E148)</f>
@@ -6073,7 +6692,7 @@
         <f>IF(F148="Pago","Pago",IF(G148=0,"A vencer",IF(G148&lt;=30,"1-30",IF(G148&lt;=60,"31-60",IF(G148&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I148" s="18">
+      <c r="I148" s="28">
         <f>IF(F148="Pago",1,IF(G148=0,0.97,IF(G148&lt;=30,0.9,IF(G148&lt;=60,0.72,IF(G148&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -6091,8 +6710,8 @@
       <c r="A149" s="14" t="n"/>
       <c r="B149" s="14" t="n"/>
       <c r="C149" s="15" t="n"/>
-      <c r="D149" s="17" t="n"/>
-      <c r="E149" s="17" t="n"/>
+      <c r="D149" s="27" t="n"/>
+      <c r="E149" s="27" t="n"/>
       <c r="F149" s="14" t="n"/>
       <c r="G149" s="14">
         <f>IF(OR(F149="Pago",E149="",E149&gt;=TODAY()),0,TODAY()-E149)</f>
@@ -6102,7 +6721,7 @@
         <f>IF(F149="Pago","Pago",IF(G149=0,"A vencer",IF(G149&lt;=30,"1-30",IF(G149&lt;=60,"31-60",IF(G149&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I149" s="18">
+      <c r="I149" s="28">
         <f>IF(F149="Pago",1,IF(G149=0,0.97,IF(G149&lt;=30,0.9,IF(G149&lt;=60,0.72,IF(G149&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -6120,8 +6739,8 @@
       <c r="A150" s="14" t="n"/>
       <c r="B150" s="14" t="n"/>
       <c r="C150" s="15" t="n"/>
-      <c r="D150" s="17" t="n"/>
-      <c r="E150" s="17" t="n"/>
+      <c r="D150" s="27" t="n"/>
+      <c r="E150" s="27" t="n"/>
       <c r="F150" s="14" t="n"/>
       <c r="G150" s="14">
         <f>IF(OR(F150="Pago",E150="",E150&gt;=TODAY()),0,TODAY()-E150)</f>
@@ -6131,7 +6750,7 @@
         <f>IF(F150="Pago","Pago",IF(G150=0,"A vencer",IF(G150&lt;=30,"1-30",IF(G150&lt;=60,"31-60",IF(G150&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I150" s="18">
+      <c r="I150" s="28">
         <f>IF(F150="Pago",1,IF(G150=0,0.97,IF(G150&lt;=30,0.9,IF(G150&lt;=60,0.72,IF(G150&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -6149,8 +6768,8 @@
       <c r="A151" s="14" t="n"/>
       <c r="B151" s="14" t="n"/>
       <c r="C151" s="15" t="n"/>
-      <c r="D151" s="17" t="n"/>
-      <c r="E151" s="17" t="n"/>
+      <c r="D151" s="27" t="n"/>
+      <c r="E151" s="27" t="n"/>
       <c r="F151" s="14" t="n"/>
       <c r="G151" s="14">
         <f>IF(OR(F151="Pago",E151="",E151&gt;=TODAY()),0,TODAY()-E151)</f>
@@ -6160,7 +6779,7 @@
         <f>IF(F151="Pago","Pago",IF(G151=0,"A vencer",IF(G151&lt;=30,"1-30",IF(G151&lt;=60,"31-60",IF(G151&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I151" s="18">
+      <c r="I151" s="28">
         <f>IF(F151="Pago",1,IF(G151=0,0.97,IF(G151&lt;=30,0.9,IF(G151&lt;=60,0.72,IF(G151&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -6178,8 +6797,8 @@
       <c r="A152" s="14" t="n"/>
       <c r="B152" s="14" t="n"/>
       <c r="C152" s="15" t="n"/>
-      <c r="D152" s="17" t="n"/>
-      <c r="E152" s="17" t="n"/>
+      <c r="D152" s="27" t="n"/>
+      <c r="E152" s="27" t="n"/>
       <c r="F152" s="14" t="n"/>
       <c r="G152" s="14">
         <f>IF(OR(F152="Pago",E152="",E152&gt;=TODAY()),0,TODAY()-E152)</f>
@@ -6189,7 +6808,7 @@
         <f>IF(F152="Pago","Pago",IF(G152=0,"A vencer",IF(G152&lt;=30,"1-30",IF(G152&lt;=60,"31-60",IF(G152&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I152" s="18">
+      <c r="I152" s="28">
         <f>IF(F152="Pago",1,IF(G152=0,0.97,IF(G152&lt;=30,0.9,IF(G152&lt;=60,0.72,IF(G152&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -6207,8 +6826,8 @@
       <c r="A153" s="14" t="n"/>
       <c r="B153" s="14" t="n"/>
       <c r="C153" s="15" t="n"/>
-      <c r="D153" s="17" t="n"/>
-      <c r="E153" s="17" t="n"/>
+      <c r="D153" s="27" t="n"/>
+      <c r="E153" s="27" t="n"/>
       <c r="F153" s="14" t="n"/>
       <c r="G153" s="14">
         <f>IF(OR(F153="Pago",E153="",E153&gt;=TODAY()),0,TODAY()-E153)</f>
@@ -6218,7 +6837,7 @@
         <f>IF(F153="Pago","Pago",IF(G153=0,"A vencer",IF(G153&lt;=30,"1-30",IF(G153&lt;=60,"31-60",IF(G153&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I153" s="18">
+      <c r="I153" s="28">
         <f>IF(F153="Pago",1,IF(G153=0,0.97,IF(G153&lt;=30,0.9,IF(G153&lt;=60,0.72,IF(G153&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -6236,8 +6855,8 @@
       <c r="A154" s="14" t="n"/>
       <c r="B154" s="14" t="n"/>
       <c r="C154" s="15" t="n"/>
-      <c r="D154" s="17" t="n"/>
-      <c r="E154" s="17" t="n"/>
+      <c r="D154" s="27" t="n"/>
+      <c r="E154" s="27" t="n"/>
       <c r="F154" s="14" t="n"/>
       <c r="G154" s="14">
         <f>IF(OR(F154="Pago",E154="",E154&gt;=TODAY()),0,TODAY()-E154)</f>
@@ -6247,7 +6866,7 @@
         <f>IF(F154="Pago","Pago",IF(G154=0,"A vencer",IF(G154&lt;=30,"1-30",IF(G154&lt;=60,"31-60",IF(G154&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I154" s="18">
+      <c r="I154" s="28">
         <f>IF(F154="Pago",1,IF(G154=0,0.97,IF(G154&lt;=30,0.9,IF(G154&lt;=60,0.72,IF(G154&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -6265,8 +6884,8 @@
       <c r="A155" s="14" t="n"/>
       <c r="B155" s="14" t="n"/>
       <c r="C155" s="15" t="n"/>
-      <c r="D155" s="17" t="n"/>
-      <c r="E155" s="17" t="n"/>
+      <c r="D155" s="27" t="n"/>
+      <c r="E155" s="27" t="n"/>
       <c r="F155" s="14" t="n"/>
       <c r="G155" s="14">
         <f>IF(OR(F155="Pago",E155="",E155&gt;=TODAY()),0,TODAY()-E155)</f>
@@ -6276,7 +6895,7 @@
         <f>IF(F155="Pago","Pago",IF(G155=0,"A vencer",IF(G155&lt;=30,"1-30",IF(G155&lt;=60,"31-60",IF(G155&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I155" s="18">
+      <c r="I155" s="28">
         <f>IF(F155="Pago",1,IF(G155=0,0.97,IF(G155&lt;=30,0.9,IF(G155&lt;=60,0.72,IF(G155&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -6294,8 +6913,8 @@
       <c r="A156" s="14" t="n"/>
       <c r="B156" s="14" t="n"/>
       <c r="C156" s="15" t="n"/>
-      <c r="D156" s="17" t="n"/>
-      <c r="E156" s="17" t="n"/>
+      <c r="D156" s="27" t="n"/>
+      <c r="E156" s="27" t="n"/>
       <c r="F156" s="14" t="n"/>
       <c r="G156" s="14">
         <f>IF(OR(F156="Pago",E156="",E156&gt;=TODAY()),0,TODAY()-E156)</f>
@@ -6305,7 +6924,7 @@
         <f>IF(F156="Pago","Pago",IF(G156=0,"A vencer",IF(G156&lt;=30,"1-30",IF(G156&lt;=60,"31-60",IF(G156&lt;=90,"61-90","90+")))))</f>
         <v/>
       </c>
-      <c r="I156" s="18">
+      <c r="I156" s="28">
         <f>IF(F156="Pago",1,IF(G156=0,0.97,IF(G156&lt;=30,0.9,IF(G156&lt;=60,0.72,IF(G156&lt;=90,0.5,0.25)))))</f>
         <v/>
       </c>
@@ -6954,7 +7573,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K6:K156">
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="2">
       <formula>"Escalar / jurídico"</formula>
     </cfRule>
   </conditionalFormatting>
